--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -117,11 +117,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -153,6 +197,8 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:K197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -547,46 +593,58 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>model_number
+（型番）</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>series_en
 （シリーズ英字）</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>series_kana
 （シリーズカナ）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>category_id
 （カテゴリ番号）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gender
 （性別）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>type
 （種別）</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>keywords
 （別名・キーワード）</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>notes
 （備考）</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>additional_word
+（追加単語）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -594,14 +652,16 @@
           <t>【セイコー】</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="13" t="n"/>
+      <c r="H2" s="13" t="n"/>
+      <c r="I2" s="13" t="n"/>
+      <c r="J2" s="13" t="n"/>
+      <c r="K2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -614,33 +674,34 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>GRAND SEIKO</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>グランドセイコー</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>2084053754</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -653,29 +714,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>DOLCE</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>ドルチェ</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2084053755</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -688,29 +750,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>EXCELINE</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>エクセリーヌ</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2084053756</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -723,37 +786,38 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>LUKIA</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>ルキア</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>2084053757</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>LK</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -766,29 +830,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>BRIGHTZ</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>ブライツ</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>2084053758</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -801,29 +866,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>CREDOR</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>クレドール</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2084054005</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -836,33 +902,34 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>SPIRIT</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>スピリット</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2084211407</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
           <t>SPILIT</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>※ヤフオク表記「SPILIT」</t>
         </is>
@@ -879,29 +946,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>WIRED</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ワイアード</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2084211408</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -914,29 +982,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>PROSPEX</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>プロスペックス</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2084211409</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -949,29 +1018,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>IGNITION</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>イグニッション</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2084211410</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -984,29 +1054,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>ALBA</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>アルバ</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2084217133</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1019,29 +1090,30 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>2084053759</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -1053,14 +1125,16 @@
           <t>【シチズン】</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1073,29 +1147,30 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ATTESA</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>アテッサ</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2084209455</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1108,37 +1183,38 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>WICCA</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>ウィッカ</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2084209458</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
           <t>Wicca</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1151,29 +1227,30 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>EXCEED</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>エクシード</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>2084209454</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1186,29 +1263,30 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Q&amp;Q</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>キューアンドキュー</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2084314563</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1221,33 +1299,34 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>クロスシー</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2084209457</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1260,29 +1339,30 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>PROMASTER</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>プロマスター</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2084209456</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1295,29 +1375,30 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>REGUNO</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>レグノ</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2084314562</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1330,29 +1411,30 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>2084209459</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -1364,14 +1446,16 @@
           <t>【カシオ】</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="13" t="n"/>
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1384,33 +1468,34 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>PRO TREK</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>プロトレック</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2084032116</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
           <t>PROTREK</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1423,29 +1508,30 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>OCEANUS</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>オシアナス</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2084211406</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1458,29 +1544,30 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>EDIFICE</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>エディフィス</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2084310827</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1493,29 +1580,30 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>DATA BANK</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>データバンク</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2084226882</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1528,29 +1616,30 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>2084032138</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -1562,14 +1651,16 @@
           <t>【G-SHOCK】※ヤフオクではカシオと別カテゴリ</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1582,29 +1673,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>GIEZ</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>ジーズ</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>2084041606</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1617,29 +1709,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>MR-G</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>MR-G</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2084041607</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1652,29 +1745,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>MT-G</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>MT-G</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2084041608</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1687,29 +1781,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>FROGMAN</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>フロッグマン</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2084045111</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1722,29 +1817,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>MUDMAN</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>マッドマン</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2084045108</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1757,29 +1853,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>GULFMAN</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>ガルフマン</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2084045119</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1792,29 +1889,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>RISEMAN</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>ライズマン</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2084045109</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1827,29 +1925,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>TOUGH SOLAR</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>タフソーラー</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2084207807</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1862,29 +1961,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>G-LIDE</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Gライド</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2084262304</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1897,29 +1997,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Crazy Colors</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>クレイジーカラーズ</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2084262305</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1932,29 +2033,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>コラボレーションモデル</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>コラボレーションモデル</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2084262308</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1967,29 +2069,30 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>2084041610</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -2001,14 +2104,16 @@
           <t>【Baby-G】</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="13" t="n"/>
+      <c r="H43" s="13" t="n"/>
+      <c r="I43" s="13" t="n"/>
+      <c r="J43" s="13" t="n"/>
+      <c r="K43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2021,33 +2126,34 @@
           <t>Baby-G</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Tripper</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>トリッパー</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2084209445</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2060,33 +2166,34 @@
           <t>Baby-G</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Reef</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>リーフ</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2084209446</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2099,33 +2206,34 @@
           <t>Baby-G</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>2084209449</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -2137,14 +2245,16 @@
           <t>【オメガ】</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="13" t="n"/>
+      <c r="I47" s="13" t="n"/>
+      <c r="J47" s="13" t="n"/>
+      <c r="K47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2157,33 +2267,34 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>CONSTELLATION</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>コンステレーション</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2084053736</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
           <t>Constellation</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2196,33 +2307,34 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>DE VILLE</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>デビル</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2084053739</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
           <t>De Ville, DeVille</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2235,33 +2347,34 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER AQUA TERRA</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>シーマスター アクアテラ</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2084221466</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
           <t>Aqua Terra</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2274,33 +2387,34 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER PLANET OCEAN</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>シーマスター プラネットオーシャン</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2084221467</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
           <t>Planet Ocean</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2313,29 +2427,30 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER 300M</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>シーマスター 300M</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2084221468</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2348,29 +2463,30 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>シーマスター</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2084221469</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>★シーマスター系フォールバック</t>
         </is>
@@ -2387,29 +2503,30 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>SPEEDMASTER DATE</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>スピードマスター デイト</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2084221470</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2422,33 +2539,34 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>SPEEDMASTER PROFESSIONAL</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>スピードマスター プロフェッショナル</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2084221471</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
           <t>Pro, Moonwatch</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -2461,29 +2579,30 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>SPEEDMASTER</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>スピードマスター</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2084221472</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>★スピマス系フォールバック</t>
         </is>
@@ -2500,29 +2619,30 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>2084053740</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr"/>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr"/>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="n"/>
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -2534,14 +2654,16 @@
           <t>【ロレックス】</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
+      <c r="I58" s="13" t="n"/>
+      <c r="J58" s="13" t="n"/>
+      <c r="K58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2554,33 +2676,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>GMT MASTER</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>GMTマスター</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2084310776</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
           <t>GMT-Master, GMT Master II</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2593,33 +2716,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>AIR-KING</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>エアキング</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2084310778</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
           <t>Air King, Air-King</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2632,33 +2756,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>EXPLORER I</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>エクスプローラーI</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2084310780</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
           <t>Explorer 1</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -2671,33 +2796,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>EXPLORER II</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>エクスプローラーII</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2084310782</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G62" s="4" t="n"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
           <t>Explorer 2</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2710,29 +2836,30 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>SUBMARINER</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>サブマリーナ</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2084310784</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -2745,33 +2872,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>SEA-DWELLER</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>シードゥエラー</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2084310786</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
           <t>Sea Dweller</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2784,29 +2912,30 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>CELLINI</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>チェリーニ</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>2084024501</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2819,33 +2948,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>DAY-DATE</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>デイデイト</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2084310788</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G66" s="4" t="n"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
           <t>Day Date, Daydate</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2858,33 +2988,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>DATEJUST</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>デイトジャスト</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2084310792</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>メンズ</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>※男性用</t>
         </is>
@@ -2901,33 +3032,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>DATEJUST</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>デイトジャスト</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2084310790</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>※女性用</t>
         </is>
@@ -2944,33 +3076,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>DAYTONA</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>デイトナ</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>2084310794</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
           <t>Cosmograph Daytona</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -2983,29 +3116,30 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>MILGAUSS</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>ミルガウス</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2084024500</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="n"/>
+      <c r="J70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -3018,33 +3152,34 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>YACHT-MASTER</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>ヨットマスター</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>2084024498</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
           <t>Yacht Master, Yachtmaster</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -3057,29 +3192,30 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>CAMELEON</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>カメレオン</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2084024502</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3092,29 +3228,30 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>2084024489</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr"/>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr"/>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="n"/>
+      <c r="J73" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3126,14 +3263,16 @@
           <t>【IWC】</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="n"/>
+      <c r="B74" s="13" t="n"/>
+      <c r="C74" s="13" t="n"/>
+      <c r="D74" s="13" t="n"/>
+      <c r="E74" s="13" t="n"/>
+      <c r="F74" s="13" t="n"/>
+      <c r="G74" s="13" t="n"/>
+      <c r="H74" s="13" t="n"/>
+      <c r="I74" s="13" t="n"/>
+      <c r="J74" s="13" t="n"/>
+      <c r="K74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -3146,29 +3285,30 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>AQUATIMER</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>アクアタイマー</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2084303663</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -3181,33 +3321,34 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>INGENIEUR</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>インヂュニア</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2084303664</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
           <t>Ingenieur</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3220,33 +3361,34 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>DA VINCI</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>ダ・ヴィンチ</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2084303666</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G77" s="4" t="n"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
           <t>Da Vinci</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -3259,33 +3401,34 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>PILOT WATCH</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>パイロット・ウォッチ</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2084303667</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G78" s="4" t="n"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
           <t>Pilot, Flieger</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr"/>
+      <c r="J78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3298,29 +3441,30 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>PORTOFINO</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>ポートフィノ</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>2084303668</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -3333,33 +3477,34 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>PORTUGIESER</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>ポルトギーゼ</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2084303669</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
           <t>Portuguese</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -3372,29 +3517,30 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>2084303695</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr"/>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr"/>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="n"/>
+      <c r="J81" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3406,14 +3552,16 @@
           <t>【タグ・ホイヤー】</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n"/>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="13" t="n"/>
+      <c r="I82" s="13" t="n"/>
+      <c r="J82" s="13" t="n"/>
+      <c r="K82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -3426,29 +3574,30 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>AQUARACER</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>アクアレーサー</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>2084262302</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -3461,29 +3610,30 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>CARRERA</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>カレラ</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>2084221480</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="n"/>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="n"/>
+      <c r="J84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -3496,33 +3646,34 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>FORMULA 1</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>フォーミュラ</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2084262301</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G85" s="4" t="n"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
           <t>Formula, F1</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr"/>
+      <c r="J85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -3535,29 +3686,30 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>MONACO</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>モナコ</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>2084221479</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="n"/>
+      <c r="J86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -3570,29 +3722,30 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>LINK</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>リンク</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>2084221481</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="n"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="n"/>
+      <c r="J87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -3605,29 +3758,30 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>2000 SERIES</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>2000シリーズ</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>2084262303</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="n"/>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="n"/>
+      <c r="J88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -3640,29 +3794,30 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>2084221482</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr"/>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr"/>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="G89" s="6" t="n"/>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="n"/>
+      <c r="J89" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3674,14 +3829,16 @@
           <t>【ハミルトン】</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n"/>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
-      <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="n"/>
+      <c r="B90" s="13" t="n"/>
+      <c r="C90" s="13" t="n"/>
+      <c r="D90" s="13" t="n"/>
+      <c r="E90" s="13" t="n"/>
+      <c r="F90" s="13" t="n"/>
+      <c r="G90" s="13" t="n"/>
+      <c r="H90" s="13" t="n"/>
+      <c r="I90" s="13" t="n"/>
+      <c r="J90" s="13" t="n"/>
+      <c r="K90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -3694,29 +3851,30 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>KHAKI</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>カーキ</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>2084221485</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="n"/>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="n"/>
+      <c r="J91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -3729,29 +3887,30 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>JAZZMASTER</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>ジャズマスター</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>2084221487</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="n"/>
+      <c r="J92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3764,29 +3923,30 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>VENTURA</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>ベンチュラ</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>2084221486</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr"/>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -3799,29 +3959,30 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>LLOYD</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>ロイド</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>2084221488</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -3834,29 +3995,30 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>2084221489</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr"/>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H95" s="6" t="inlineStr"/>
-      <c r="I95" s="6" t="inlineStr">
+      <c r="G95" s="6" t="n"/>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="n"/>
+      <c r="J95" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3868,14 +4030,16 @@
           <t>【オリエント】</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n"/>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="n"/>
-      <c r="I96" s="2" t="n"/>
+      <c r="B96" s="13" t="n"/>
+      <c r="C96" s="13" t="n"/>
+      <c r="D96" s="13" t="n"/>
+      <c r="E96" s="13" t="n"/>
+      <c r="F96" s="13" t="n"/>
+      <c r="G96" s="13" t="n"/>
+      <c r="H96" s="13" t="n"/>
+      <c r="I96" s="13" t="n"/>
+      <c r="J96" s="13" t="n"/>
+      <c r="K96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3888,29 +4052,30 @@
           <t>オリエント</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>ORIENT STAR</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>オリエントスター</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>2084211535</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -3923,29 +4088,30 @@
           <t>オリエント</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>KING MASTER</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>キングマスター</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>2084211536</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="n"/>
+      <c r="J98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -3958,29 +4124,30 @@
           <t>オリエント</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>2084211537</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr"/>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H99" s="6" t="inlineStr"/>
-      <c r="I99" s="6" t="inlineStr">
+      <c r="G99" s="6" t="n"/>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="n"/>
+      <c r="J99" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3992,14 +4159,16 @@
           <t>【ロンジン】</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n"/>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="n"/>
+      <c r="B100" s="13" t="n"/>
+      <c r="C100" s="13" t="n"/>
+      <c r="D100" s="13" t="n"/>
+      <c r="E100" s="13" t="n"/>
+      <c r="F100" s="13" t="n"/>
+      <c r="G100" s="13" t="n"/>
+      <c r="H100" s="13" t="n"/>
+      <c r="I100" s="13" t="n"/>
+      <c r="J100" s="13" t="n"/>
+      <c r="K100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -4012,29 +4181,30 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>ADMIRAL</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>アドミラル</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>2084308400</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="n"/>
+      <c r="J101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -4047,29 +4217,30 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>GRAND CLASSIC</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>グランドクラシック</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>2084308401</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -4082,29 +4253,30 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>CONQUEST</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>コンクエスト</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>2084308402</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr"/>
-      <c r="I103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -4117,29 +4289,30 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>DOLCE VITA</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>ドルチェビータ</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>2084308403</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -4152,33 +4325,34 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>HYDROCONQUEST</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>ハイドロ コンクエスト</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>2084308404</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G105" s="4" t="n"/>
       <c r="H105" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
           <t>Hydro Conquest</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -4191,29 +4365,30 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>2084308405</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr"/>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr"/>
-      <c r="I106" s="6" t="inlineStr">
+      <c r="G106" s="6" t="n"/>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="n"/>
+      <c r="J106" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -4225,14 +4400,16 @@
           <t>【カルティエ】</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n"/>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
+      <c r="B107" s="13" t="n"/>
+      <c r="C107" s="13" t="n"/>
+      <c r="D107" s="13" t="n"/>
+      <c r="E107" s="13" t="n"/>
+      <c r="F107" s="13" t="n"/>
+      <c r="G107" s="13" t="n"/>
+      <c r="H107" s="13" t="n"/>
+      <c r="I107" s="13" t="n"/>
+      <c r="J107" s="13" t="n"/>
+      <c r="K107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -4245,33 +4422,34 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>SANTOS</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>サントス</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>2084053718</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr"/>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G108" s="4" t="n"/>
       <c r="H108" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
           <t>Santos de Cartier</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -4284,33 +4462,34 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>PANTHERE</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>パンテール</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>2084053720</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G109" s="4" t="n"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
           <t>Panthere de Cartier</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr"/>
+      <c r="J109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -4323,29 +4502,30 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="inlineStr">
         <is>
           <t>BAIGNOIRE</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>ベニュワール</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>2084053721</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr"/>
-      <c r="I110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="n"/>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="n"/>
+      <c r="J110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -4358,29 +4538,30 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>RANIERE</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>ラニエール</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>2084053722</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr"/>
-      <c r="I111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="n"/>
+      <c r="J111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -4393,29 +4574,30 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>ROADSTER</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>ロードスター</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
+      <c r="F112" s="4" t="inlineStr">
         <is>
           <t>2084053719</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr"/>
-      <c r="I112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -4428,33 +4610,34 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>TANK FRANCAISE</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>タンクフランセーズ</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>2084053728</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G113" s="4" t="n"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
           <t>Tank Française</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr"/>
+      <c r="J113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -4467,33 +4650,34 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>TANK AMERICAINE</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>タンクアメリカン</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>2084053729</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G114" s="4" t="n"/>
       <c r="H114" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
           <t>Tank American</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -4506,29 +4690,30 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>MUST TANK</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>マストタンク</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>2084053730</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr"/>
-      <c r="I115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -4541,33 +4726,34 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>PASHA</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>パシャ</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>2084053724</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr"/>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G116" s="4" t="n"/>
       <c r="H116" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
           <t>Pasha C, Pasha de Cartier</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr"/>
+      <c r="J116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -4580,29 +4766,30 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <t>2084053723</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr"/>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="inlineStr"/>
-      <c r="I117" s="6" t="inlineStr">
+      <c r="G117" s="6" t="n"/>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="n"/>
+      <c r="J117" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -4614,14 +4801,16 @@
           <t>【ブルガリ】</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
+      <c r="B118" s="13" t="n"/>
+      <c r="C118" s="13" t="n"/>
+      <c r="D118" s="13" t="n"/>
+      <c r="E118" s="13" t="n"/>
+      <c r="F118" s="13" t="n"/>
+      <c r="G118" s="13" t="n"/>
+      <c r="H118" s="13" t="n"/>
+      <c r="I118" s="13" t="n"/>
+      <c r="J118" s="13" t="n"/>
+      <c r="K118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -4634,29 +4823,30 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>ASSIOMA</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>アショーマ</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>2084285566</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr"/>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr"/>
-      <c r="I119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="n"/>
+      <c r="J119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -4669,33 +4859,34 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>ALUMINIUM</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>アルミニウム</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>2084053746</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G120" s="4" t="n"/>
       <c r="H120" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
           <t>Aluminum</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr"/>
+      <c r="J120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -4708,29 +4899,30 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>ERGON</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>エルゴン</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>2084285567</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr"/>
-      <c r="I121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -4743,29 +4935,30 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>DIAGONO</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="E122" s="4" t="inlineStr">
         <is>
           <t>ディアゴノ</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>2084053749</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr"/>
-      <c r="I122" s="4" t="inlineStr"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -4778,33 +4971,34 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>B.ZERO1</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>ビーゼロワン</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>2084053747</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr"/>
-      <c r="G123" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G123" s="4" t="n"/>
       <c r="H123" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
           <t>B-Zero1, BZero1</t>
         </is>
       </c>
-      <c r="I123" s="4" t="inlineStr"/>
+      <c r="J123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -4817,33 +5011,34 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>BVLGARI BVLGARI</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="E124" s="4" t="inlineStr">
         <is>
           <t>ブルガリブルガリ</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>2084053748</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G124" s="4" t="n"/>
       <c r="H124" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -4856,29 +5051,30 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>SOLOTEMPO</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>ソロテンポ</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>2084053752</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr"/>
-      <c r="I125" s="4" t="inlineStr"/>
+      <c r="G125" s="4" t="n"/>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="n"/>
+      <c r="J125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -4891,29 +5087,30 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C126" s="4" t="n"/>
+      <c r="D126" s="4" t="inlineStr">
         <is>
           <t>RETTANGOLO</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="E126" s="4" t="inlineStr">
         <is>
           <t>レッタンゴロ</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>2084053751</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr"/>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr"/>
-      <c r="I126" s="4" t="inlineStr"/>
+      <c r="G126" s="4" t="n"/>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="n"/>
+      <c r="J126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -4926,29 +5123,30 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <t>2084053753</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H127" s="6" t="inlineStr"/>
-      <c r="I127" s="6" t="inlineStr">
+      <c r="G127" s="6" t="n"/>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="n"/>
+      <c r="J127" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -4960,14 +5158,16 @@
           <t>【その他ブランド（シリーズなし）】</t>
         </is>
       </c>
-      <c r="B128" s="2" t="n"/>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="n"/>
-      <c r="F128" s="2" t="n"/>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="n"/>
-      <c r="I128" s="2" t="n"/>
+      <c r="B128" s="13" t="n"/>
+      <c r="C128" s="13" t="n"/>
+      <c r="D128" s="13" t="n"/>
+      <c r="E128" s="13" t="n"/>
+      <c r="F128" s="13" t="n"/>
+      <c r="G128" s="13" t="n"/>
+      <c r="H128" s="13" t="n"/>
+      <c r="I128" s="13" t="n"/>
+      <c r="J128" s="13" t="n"/>
+      <c r="K128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
@@ -4980,17 +5180,18 @@
           <t>ディーゼル</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr"/>
-      <c r="D129" s="8" t="inlineStr"/>
-      <c r="E129" s="8" t="inlineStr"/>
-      <c r="F129" s="8" t="inlineStr"/>
-      <c r="G129" s="8" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H129" s="8" t="inlineStr"/>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="8" t="n"/>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="n"/>
+      <c r="J129" s="8" t="inlineStr">
         <is>
           <t>★性別不明→空白（Q1）</t>
         </is>
@@ -5007,17 +5208,18 @@
           <t>グッチ</t>
         </is>
       </c>
-      <c r="C130" s="8" t="inlineStr"/>
-      <c r="D130" s="8" t="inlineStr"/>
-      <c r="E130" s="8" t="inlineStr"/>
-      <c r="F130" s="8" t="inlineStr"/>
-      <c r="G130" s="8" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H130" s="8" t="inlineStr"/>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="C130" s="8" t="n"/>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="8" t="n"/>
+      <c r="G130" s="8" t="n"/>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I130" s="8" t="n"/>
+      <c r="J130" s="8" t="inlineStr">
         <is>
           <t>★性別不明→空白（Q1）</t>
         </is>
@@ -5034,29 +5236,30 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>H WATCH</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Hウォッチ</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>2084209450</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr"/>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr"/>
-      <c r="I131" s="4" t="inlineStr"/>
+      <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="n"/>
+      <c r="J131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -5069,29 +5272,30 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>CLIPPER</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>クリッパー</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>2084209451</t>
         </is>
       </c>
-      <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr"/>
-      <c r="I132" s="4" t="inlineStr"/>
+      <c r="G132" s="4" t="n"/>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="n"/>
+      <c r="J132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -5104,29 +5308,30 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t>KELLY</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t>ケリー</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="F133" s="4" t="inlineStr">
         <is>
           <t>2084209452</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr"/>
-      <c r="G133" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="inlineStr"/>
-      <c r="I133" s="4" t="inlineStr"/>
+      <c r="G133" s="4" t="n"/>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="n"/>
+      <c r="J133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -5139,29 +5344,30 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="C134" s="6" t="n"/>
+      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <t>2084209453</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr"/>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr"/>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="G134" s="6" t="n"/>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="n"/>
+      <c r="J134" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5178,29 +5384,30 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>NAVITIMER</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="E135" s="4" t="inlineStr">
         <is>
           <t>ナビタイマー</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>2084221499</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr"/>
-      <c r="I135" s="4" t="inlineStr"/>
+      <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -5213,33 +5420,34 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>CHRONOMAT</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>クロノマット</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>2084221495</t>
         </is>
       </c>
-      <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G136" s="4" t="n"/>
       <c r="H136" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
           <t>Chronomat Evolution</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr"/>
+      <c r="J136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -5252,33 +5460,34 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>SUPEROCEAN</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="E137" s="4" t="inlineStr">
         <is>
           <t>スーパーオーシャン</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>2084221497</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr"/>
-      <c r="G137" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G137" s="4" t="n"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
           <t>Super Ocean</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -5291,29 +5500,30 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <t>2084221494</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr"/>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr"/>
-      <c r="I138" s="6" t="inlineStr">
+      <c r="G138" s="6" t="n"/>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="n"/>
+      <c r="J138" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5330,29 +5540,30 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>CASABLANCA</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>カサブランカ</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="F139" s="4" t="inlineStr">
         <is>
           <t>2084053743</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr"/>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr"/>
-      <c r="I139" s="4" t="inlineStr"/>
+      <c r="G139" s="4" t="n"/>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="n"/>
+      <c r="J139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -5365,29 +5576,30 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>CONQUISTADOR</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>コンキスタドール</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>2084053741</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr"/>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr"/>
-      <c r="I140" s="4" t="inlineStr"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="n"/>
+      <c r="J140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -5400,29 +5612,30 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>LONG ISLAND</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="E141" s="4" t="inlineStr">
         <is>
           <t>ロングアイランド</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>2084053742</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr"/>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="inlineStr"/>
-      <c r="I141" s="4" t="inlineStr"/>
+      <c r="G141" s="4" t="n"/>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="n"/>
+      <c r="J141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -5435,29 +5648,30 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="E142" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <t>2084053745</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr"/>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr"/>
-      <c r="I142" s="6" t="inlineStr">
+      <c r="G142" s="6" t="n"/>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="n"/>
+      <c r="J142" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5474,29 +5688,30 @@
           <t>チュードル</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>SUBMARINER</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="E143" s="4" t="inlineStr">
         <is>
           <t>サブマリーナ</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>2084303672</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr"/>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr"/>
-      <c r="I143" s="4" t="inlineStr"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -5509,29 +5724,30 @@
           <t>チュードル</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>RANGER</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>レンジャー</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>2084303674</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr"/>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr"/>
-      <c r="I144" s="4" t="inlineStr"/>
+      <c r="G144" s="4" t="n"/>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="n"/>
+      <c r="J144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -5544,29 +5760,30 @@
           <t>チュードル</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="E145" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <t>2084303675</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr"/>
-      <c r="G145" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H145" s="6" t="inlineStr"/>
-      <c r="I145" s="6" t="inlineStr">
+      <c r="G145" s="6" t="n"/>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="n"/>
+      <c r="J145" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5583,29 +5800,30 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>LUMINOR BASE</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>ルミノール ベース</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>2084221473</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr"/>
-      <c r="G146" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr"/>
-      <c r="I146" s="4" t="inlineStr"/>
+      <c r="G146" s="4" t="n"/>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="n"/>
+      <c r="J146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -5618,29 +5836,30 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="4" t="inlineStr">
         <is>
           <t>LUMINOR MARINA</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="E147" s="4" t="inlineStr">
         <is>
           <t>ルミノール マリーナ</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>2084221474</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr"/>
-      <c r="G147" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H147" s="4" t="inlineStr"/>
-      <c r="I147" s="4" t="inlineStr"/>
+      <c r="G147" s="4" t="n"/>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="n"/>
+      <c r="J147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -5653,29 +5872,30 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>RADIOMIR</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>ラジオミール</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>2084221475</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr"/>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr"/>
-      <c r="I148" s="4" t="inlineStr"/>
+      <c r="G148" s="4" t="n"/>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="n"/>
+      <c r="J148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -5688,29 +5908,30 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <t>2084221476</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr"/>
-      <c r="G149" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H149" s="6" t="inlineStr"/>
-      <c r="I149" s="6" t="inlineStr">
+      <c r="G149" s="6" t="n"/>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="n"/>
+      <c r="J149" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5727,29 +5948,30 @@
           <t>シャネル</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>J12</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>J12</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
+      <c r="F150" s="4" t="inlineStr">
         <is>
           <t>2084308389</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr"/>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr"/>
-      <c r="I150" s="4" t="inlineStr"/>
+      <c r="G150" s="4" t="n"/>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="n"/>
+      <c r="J150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -5762,29 +5984,30 @@
           <t>シャネル</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="4" t="inlineStr">
         <is>
           <t>PREMIERE</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="E151" s="4" t="inlineStr">
         <is>
           <t>プルミエール</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="F151" s="4" t="inlineStr">
         <is>
           <t>2084308390</t>
         </is>
       </c>
-      <c r="F151" s="4" t="inlineStr"/>
-      <c r="G151" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H151" s="4" t="inlineStr"/>
-      <c r="I151" s="4" t="inlineStr"/>
+      <c r="G151" s="4" t="n"/>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="n"/>
+      <c r="J151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -5797,29 +6020,30 @@
           <t>シャネル</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="E152" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <t>2084308394</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr"/>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H152" s="6" t="inlineStr"/>
-      <c r="I152" s="6" t="inlineStr">
+      <c r="G152" s="6" t="n"/>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="n"/>
+      <c r="J152" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5836,29 +6060,30 @@
           <t>ルミノックス</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="E153" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <t>2084221504</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr"/>
-      <c r="G153" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H153" s="6" t="inlineStr"/>
-      <c r="I153" s="6" t="inlineStr">
+      <c r="G153" s="6" t="n"/>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="n"/>
+      <c r="J153" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5875,29 +6100,30 @@
           <t>ニクソン</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="E154" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <t>2084308399</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr"/>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H154" s="6" t="inlineStr"/>
-      <c r="I154" s="6" t="inlineStr">
+      <c r="G154" s="6" t="n"/>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="n"/>
+      <c r="J154" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5914,33 +6140,34 @@
           <t>ガガミラノ</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C155" s="4" t="n"/>
+      <c r="D155" s="4" t="inlineStr">
         <is>
           <t>MANUALE</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="E155" s="4" t="inlineStr">
         <is>
           <t>マニュアーレ</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
+      <c r="F155" s="4" t="inlineStr">
         <is>
           <t>2084303679</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr"/>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G155" s="4" t="n"/>
       <c r="H155" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
           <t>GaGa MILANO</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr"/>
+      <c r="J155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -5953,33 +6180,34 @@
           <t>ガガミラノ</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="E156" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <t>2084303681</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr"/>
-      <c r="G156" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G156" s="6" t="n"/>
       <c r="H156" s="6" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
           <t>GaGa MILANO</t>
         </is>
       </c>
-      <c r="I156" s="6" t="inlineStr">
+      <c r="J156" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5996,29 +6224,30 @@
           <t>スウォッチ</t>
         </is>
       </c>
-      <c r="C157" s="4" t="inlineStr">
+      <c r="C157" s="4" t="n"/>
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t>CHRONO</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr">
+      <c r="E157" s="4" t="inlineStr">
         <is>
           <t>クロノ</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
+      <c r="F157" s="4" t="inlineStr">
         <is>
           <t>2084024477</t>
         </is>
       </c>
-      <c r="F157" s="4" t="inlineStr"/>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr"/>
-      <c r="I157" s="4" t="inlineStr"/>
+      <c r="G157" s="4" t="n"/>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="n"/>
+      <c r="J157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -6031,29 +6260,30 @@
           <t>スウォッチ</t>
         </is>
       </c>
-      <c r="C158" s="4" t="inlineStr">
+      <c r="C158" s="4" t="n"/>
+      <c r="D158" s="4" t="inlineStr">
         <is>
           <t>IRONY</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="E158" s="4" t="inlineStr">
         <is>
           <t>アイロニー</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>2084024486</t>
         </is>
       </c>
-      <c r="F158" s="4" t="inlineStr"/>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
-      <c r="I158" s="4" t="inlineStr"/>
+      <c r="G158" s="4" t="n"/>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="n"/>
+      <c r="J158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -6066,29 +6296,30 @@
           <t>スウォッチ</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
+      <c r="C159" s="6" t="n"/>
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <t>2084024488</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr"/>
-      <c r="G159" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H159" s="6" t="inlineStr"/>
-      <c r="I159" s="6" t="inlineStr">
+      <c r="G159" s="6" t="n"/>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="n"/>
+      <c r="J159" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -6100,14 +6331,16 @@
           <t>【1カテゴリブランド】</t>
         </is>
       </c>
-      <c r="B160" s="2" t="n"/>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" s="2" t="n"/>
-      <c r="F160" s="2" t="n"/>
-      <c r="G160" s="2" t="n"/>
-      <c r="H160" s="2" t="n"/>
-      <c r="I160" s="2" t="n"/>
+      <c r="B160" s="13" t="n"/>
+      <c r="C160" s="13" t="n"/>
+      <c r="D160" s="13" t="n"/>
+      <c r="E160" s="13" t="n"/>
+      <c r="F160" s="13" t="n"/>
+      <c r="G160" s="13" t="n"/>
+      <c r="H160" s="13" t="n"/>
+      <c r="I160" s="13" t="n"/>
+      <c r="J160" s="13" t="n"/>
+      <c r="K160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -6120,29 +6353,30 @@
           <t>ティソ</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
+      <c r="C161" s="4" t="n"/>
+      <c r="D161" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="E161" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
+      <c r="F161" s="4" t="inlineStr">
         <is>
           <t>2084061410</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr"/>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr"/>
-      <c r="I161" s="4" t="inlineStr"/>
+      <c r="G161" s="4" t="n"/>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="n"/>
+      <c r="J161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -6155,29 +6389,30 @@
           <t>ゼニス</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr">
+      <c r="C162" s="4" t="n"/>
+      <c r="D162" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="E162" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>2084024517</t>
         </is>
       </c>
-      <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr"/>
-      <c r="I162" s="4" t="inlineStr"/>
+      <c r="G162" s="4" t="n"/>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="n"/>
+      <c r="J162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -6190,29 +6425,30 @@
           <t>オリス</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="E163" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>2084024537</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H163" s="4" t="inlineStr"/>
-      <c r="I163" s="4" t="inlineStr"/>
+      <c r="G163" s="4" t="n"/>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="n"/>
+      <c r="J163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -6225,29 +6461,30 @@
           <t>ラドー</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C164" s="4" t="n"/>
+      <c r="D164" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="E164" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>2084024519</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr"/>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr"/>
-      <c r="I164" s="4" t="inlineStr"/>
+      <c r="G164" s="4" t="n"/>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="n"/>
+      <c r="J164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -6260,29 +6497,30 @@
           <t>ウブロ</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="E165" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
+      <c r="F165" s="4" t="inlineStr">
         <is>
           <t>2084212696</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr"/>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr"/>
-      <c r="I165" s="4" t="inlineStr"/>
+      <c r="G165" s="4" t="n"/>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="n"/>
+      <c r="J165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -6295,33 +6533,34 @@
           <t>オーデマ・ピゲ</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr">
+      <c r="C166" s="4" t="n"/>
+      <c r="D166" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="E166" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>2084024547</t>
         </is>
       </c>
-      <c r="F166" s="4" t="inlineStr"/>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G166" s="4" t="n"/>
       <c r="H166" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -6334,33 +6573,34 @@
           <t>ヴァシュロン・コンスタンタン</t>
         </is>
       </c>
-      <c r="C167" s="4" t="inlineStr">
+      <c r="C167" s="4" t="n"/>
+      <c r="D167" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E167" s="4" t="inlineStr">
+      <c r="F167" s="4" t="inlineStr">
         <is>
           <t>2084024530</t>
         </is>
       </c>
-      <c r="F167" s="4" t="inlineStr"/>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G167" s="4" t="n"/>
       <c r="H167" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
           <t>VC</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr"/>
+      <c r="J167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -6373,29 +6613,30 @@
           <t>ブレゲ</t>
         </is>
       </c>
-      <c r="C168" s="4" t="inlineStr">
+      <c r="C168" s="4" t="n"/>
+      <c r="D168" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>2084024521</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr"/>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr"/>
-      <c r="I168" s="4" t="inlineStr"/>
+      <c r="G168" s="4" t="n"/>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="n"/>
+      <c r="J168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -6408,29 +6649,30 @@
           <t>ブランパン</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="E169" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
+      <c r="F169" s="4" t="inlineStr">
         <is>
           <t>2084024545</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr"/>
-      <c r="G169" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H169" s="4" t="inlineStr"/>
-      <c r="I169" s="4" t="inlineStr"/>
+      <c r="G169" s="4" t="n"/>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="n"/>
+      <c r="J169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -6443,29 +6685,30 @@
           <t>ピアジェ</t>
         </is>
       </c>
-      <c r="C170" s="4" t="inlineStr">
+      <c r="C170" s="4" t="n"/>
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="E170" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E170" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>2084024525</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr"/>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr"/>
-      <c r="I170" s="4" t="inlineStr"/>
+      <c r="G170" s="4" t="n"/>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="n"/>
+      <c r="J170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -6478,33 +6721,34 @@
           <t>ジャガー・ルクルト</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
+      <c r="C171" s="4" t="n"/>
+      <c r="D171" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
+      <c r="E171" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
+      <c r="F171" s="4" t="inlineStr">
         <is>
           <t>2084024520</t>
         </is>
       </c>
-      <c r="F171" s="4" t="inlineStr"/>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G171" s="4" t="n"/>
       <c r="H171" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
           <t>JLC</t>
         </is>
       </c>
-      <c r="I171" s="4" t="inlineStr"/>
+      <c r="J171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -6517,33 +6761,34 @@
           <t>ジラール・ペルゴ</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="E172" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
+      <c r="F172" s="4" t="inlineStr">
         <is>
           <t>2084024532</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr"/>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G172" s="4" t="n"/>
       <c r="H172" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="I172" s="4" t="inlineStr"/>
+      <c r="J172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -6556,29 +6801,30 @@
           <t>ショパール</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr">
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="E173" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
+      <c r="F173" s="4" t="inlineStr">
         <is>
           <t>2084024543</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr"/>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr"/>
-      <c r="I173" s="4" t="inlineStr"/>
+      <c r="G173" s="4" t="n"/>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="n"/>
+      <c r="J173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -6591,33 +6837,34 @@
           <t>ティファニー</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr">
+      <c r="C174" s="4" t="n"/>
+      <c r="D174" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="E174" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
+      <c r="F174" s="4" t="inlineStr">
         <is>
           <t>2084024527</t>
         </is>
       </c>
-      <c r="F174" s="4" t="inlineStr"/>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G174" s="4" t="n"/>
       <c r="H174" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
           <t>Tiffany &amp; Co</t>
         </is>
       </c>
-      <c r="I174" s="4" t="inlineStr"/>
+      <c r="J174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -6630,29 +6877,30 @@
           <t>コーチ</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr">
+      <c r="C175" s="4" t="n"/>
+      <c r="D175" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="E175" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E175" s="4" t="inlineStr">
+      <c r="F175" s="4" t="inlineStr">
         <is>
           <t>2084024542</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr"/>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr"/>
-      <c r="I175" s="4" t="inlineStr"/>
+      <c r="G175" s="4" t="n"/>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="n"/>
+      <c r="J175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -6665,29 +6913,30 @@
           <t>フォッシル</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C176" s="4" t="n"/>
+      <c r="D176" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="E176" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="F176" s="4" t="inlineStr">
         <is>
           <t>2084024541</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr"/>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr"/>
-      <c r="I176" s="4" t="inlineStr"/>
+      <c r="G176" s="4" t="n"/>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="n"/>
+      <c r="J176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -6700,29 +6949,30 @@
           <t>タイメックス</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C177" s="4" t="n"/>
+      <c r="D177" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="E177" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
+      <c r="F177" s="4" t="inlineStr">
         <is>
           <t>2084024538</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr"/>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr"/>
-      <c r="I177" s="4" t="inlineStr"/>
+      <c r="G177" s="4" t="n"/>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="n"/>
+      <c r="J177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -6735,29 +6985,30 @@
           <t>スカーゲン</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="E178" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr">
+      <c r="F178" s="4" t="inlineStr">
         <is>
           <t>2084226881</t>
         </is>
       </c>
-      <c r="F178" s="4" t="inlineStr"/>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr"/>
-      <c r="I178" s="4" t="inlineStr"/>
+      <c r="G178" s="4" t="n"/>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="n"/>
+      <c r="J178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -6770,29 +7021,30 @@
           <t>スント</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr">
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="E179" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E179" s="4" t="inlineStr">
+      <c r="F179" s="4" t="inlineStr">
         <is>
           <t>2084062073</t>
         </is>
       </c>
-      <c r="F179" s="4" t="inlineStr"/>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr"/>
-      <c r="I179" s="4" t="inlineStr"/>
+      <c r="G179" s="4" t="n"/>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="n"/>
+      <c r="J179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -6805,29 +7057,30 @@
           <t>ビクトリノックス</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C180" s="4" t="n"/>
+      <c r="D180" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="E180" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
+      <c r="F180" s="4" t="inlineStr">
         <is>
           <t>2084024546</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr"/>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr"/>
-      <c r="I180" s="4" t="inlineStr"/>
+      <c r="G180" s="4" t="n"/>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="n"/>
+      <c r="J180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -6840,33 +7093,34 @@
           <t>アルマーニ</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="E181" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>2084217132</t>
         </is>
       </c>
-      <c r="F181" s="4" t="inlineStr"/>
-      <c r="G181" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G181" s="4" t="n"/>
       <c r="H181" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
           <t>EMPORIO ARMANI, GIORGIO ARMANI</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr"/>
+      <c r="J181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -6879,29 +7133,30 @@
           <t>フェンディ</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C182" s="4" t="n"/>
+      <c r="D182" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="E182" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
+      <c r="F182" s="4" t="inlineStr">
         <is>
           <t>2084024518</t>
         </is>
       </c>
-      <c r="F182" s="4" t="inlineStr"/>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr"/>
-      <c r="I182" s="4" t="inlineStr"/>
+      <c r="G182" s="4" t="n"/>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="n"/>
+      <c r="J182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -6914,29 +7169,30 @@
           <t>ダンヒル</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="E183" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E183" s="4" t="inlineStr">
+      <c r="F183" s="4" t="inlineStr">
         <is>
           <t>2084051026</t>
         </is>
       </c>
-      <c r="F183" s="4" t="inlineStr"/>
-      <c r="G183" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H183" s="4" t="inlineStr"/>
-      <c r="I183" s="4" t="inlineStr"/>
+      <c r="G183" s="4" t="n"/>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -6949,29 +7205,30 @@
           <t>ポール・スミス</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C184" s="4" t="n"/>
+      <c r="D184" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="E184" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
+      <c r="F184" s="4" t="inlineStr">
         <is>
           <t>2084061863</t>
         </is>
       </c>
-      <c r="F184" s="4" t="inlineStr"/>
-      <c r="G184" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr"/>
-      <c r="I184" s="4" t="inlineStr"/>
+      <c r="G184" s="4" t="n"/>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="n"/>
+      <c r="J184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -6984,29 +7241,30 @@
           <t>ウェンガー</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C185" s="4" t="n"/>
+      <c r="D185" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="E185" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E185" s="4" t="inlineStr">
+      <c r="F185" s="4" t="inlineStr">
         <is>
           <t>2084206922</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr"/>
-      <c r="G185" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H185" s="4" t="inlineStr"/>
-      <c r="I185" s="4" t="inlineStr"/>
+      <c r="G185" s="4" t="n"/>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="n"/>
+      <c r="J185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -7019,33 +7277,34 @@
           <t>ルイ・ヴィトン</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="E186" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E186" s="4" t="inlineStr">
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>2084051028</t>
         </is>
       </c>
-      <c r="F186" s="4" t="inlineStr"/>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G186" s="4" t="n"/>
       <c r="H186" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -7058,29 +7317,30 @@
           <t>テクノス</t>
         </is>
       </c>
-      <c r="C187" s="4" t="inlineStr">
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D187" s="4" t="inlineStr">
+      <c r="E187" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E187" s="4" t="inlineStr">
+      <c r="F187" s="4" t="inlineStr">
         <is>
           <t>2084214351</t>
         </is>
       </c>
-      <c r="F187" s="4" t="inlineStr"/>
-      <c r="G187" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H187" s="4" t="inlineStr"/>
-      <c r="I187" s="4" t="inlineStr"/>
+      <c r="G187" s="4" t="n"/>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="n"/>
+      <c r="J187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -7093,29 +7353,30 @@
           <t>エルジン</t>
         </is>
       </c>
-      <c r="C188" s="4" t="inlineStr">
+      <c r="C188" s="4" t="n"/>
+      <c r="D188" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D188" s="4" t="inlineStr">
+      <c r="E188" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
+      <c r="F188" s="4" t="inlineStr">
         <is>
           <t>2084024513</t>
         </is>
       </c>
-      <c r="F188" s="4" t="inlineStr"/>
-      <c r="G188" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H188" s="4" t="inlineStr"/>
-      <c r="I188" s="4" t="inlineStr"/>
+      <c r="G188" s="4" t="n"/>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="n"/>
+      <c r="J188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -7128,29 +7389,30 @@
           <t>ヴェルサーチ</t>
         </is>
       </c>
-      <c r="C189" s="4" t="inlineStr">
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr">
+      <c r="E189" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>2084224440</t>
         </is>
       </c>
-      <c r="F189" s="4" t="inlineStr"/>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H189" s="4" t="inlineStr"/>
-      <c r="I189" s="4" t="inlineStr"/>
+      <c r="G189" s="4" t="n"/>
+      <c r="H189" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="n"/>
+      <c r="J189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -7163,29 +7425,30 @@
           <t>モンブラン</t>
         </is>
       </c>
-      <c r="C190" s="4" t="inlineStr">
+      <c r="C190" s="4" t="n"/>
+      <c r="D190" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D190" s="4" t="inlineStr">
+      <c r="E190" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
+      <c r="F190" s="4" t="inlineStr">
         <is>
           <t>2084229201</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr"/>
-      <c r="G190" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H190" s="4" t="inlineStr"/>
-      <c r="I190" s="4" t="inlineStr"/>
+      <c r="G190" s="4" t="n"/>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="n"/>
+      <c r="J190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -7198,29 +7461,30 @@
           <t>ヴィヴィアン ウエストウッド</t>
         </is>
       </c>
-      <c r="C191" s="4" t="inlineStr">
+      <c r="C191" s="4" t="n"/>
+      <c r="D191" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D191" s="4" t="inlineStr">
+      <c r="E191" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E191" s="4" t="inlineStr">
+      <c r="F191" s="4" t="inlineStr">
         <is>
           <t>2084024531</t>
         </is>
       </c>
-      <c r="F191" s="4" t="inlineStr"/>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H191" s="4" t="inlineStr"/>
-      <c r="I191" s="4" t="inlineStr"/>
+      <c r="G191" s="4" t="n"/>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="n"/>
+      <c r="J191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -7233,33 +7497,34 @@
           <t>アニエスベー</t>
         </is>
       </c>
-      <c r="C192" s="4" t="inlineStr">
+      <c r="C192" s="4" t="n"/>
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D192" s="4" t="inlineStr">
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>2084024511</t>
         </is>
       </c>
-      <c r="F192" s="4" t="inlineStr"/>
-      <c r="G192" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G192" s="4" t="n"/>
       <c r="H192" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
           <t>agnes b.</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr"/>
+      <c r="J192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -7272,33 +7537,34 @@
           <t>アディダス</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr">
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="E193" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
+      <c r="F193" s="4" t="inlineStr">
         <is>
           <t>2084301267</t>
         </is>
       </c>
-      <c r="F193" s="4" t="inlineStr"/>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="G193" s="4" t="n"/>
       <c r="H193" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
           <t>adidas</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr"/>
+      <c r="J193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -7311,29 +7577,30 @@
           <t>ナイキ</t>
         </is>
       </c>
-      <c r="C194" s="4" t="inlineStr">
+      <c r="C194" s="4" t="n"/>
+      <c r="D194" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D194" s="4" t="inlineStr">
+      <c r="E194" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E194" s="4" t="inlineStr">
+      <c r="F194" s="4" t="inlineStr">
         <is>
           <t>2084216392</t>
         </is>
       </c>
-      <c r="F194" s="4" t="inlineStr"/>
-      <c r="G194" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr"/>
-      <c r="I194" s="4" t="inlineStr"/>
+      <c r="G194" s="4" t="n"/>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="n"/>
+      <c r="J194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -7346,29 +7613,30 @@
           <t>ポリス</t>
         </is>
       </c>
-      <c r="C195" s="4" t="inlineStr">
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D195" s="4" t="inlineStr">
+      <c r="E195" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E195" s="4" t="inlineStr">
+      <c r="F195" s="4" t="inlineStr">
         <is>
           <t>2084216393</t>
         </is>
       </c>
-      <c r="F195" s="4" t="inlineStr"/>
-      <c r="G195" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H195" s="4" t="inlineStr"/>
-      <c r="I195" s="4" t="inlineStr"/>
+      <c r="G195" s="4" t="n"/>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -7381,29 +7649,30 @@
           <t>ウォルサム</t>
         </is>
       </c>
-      <c r="C196" s="4" t="inlineStr">
+      <c r="C196" s="4" t="n"/>
+      <c r="D196" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D196" s="4" t="inlineStr">
+      <c r="E196" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E196" s="4" t="inlineStr">
+      <c r="F196" s="4" t="inlineStr">
         <is>
           <t>2084024540</t>
         </is>
       </c>
-      <c r="F196" s="4" t="inlineStr"/>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr"/>
-      <c r="I196" s="4" t="inlineStr"/>
+      <c r="G196" s="4" t="n"/>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="n"/>
+      <c r="J196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -7416,49 +7685,50 @@
           <t>ブローバ</t>
         </is>
       </c>
-      <c r="C197" s="4" t="inlineStr">
+      <c r="C197" s="4" t="n"/>
+      <c r="D197" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="D197" s="4" t="inlineStr">
+      <c r="E197" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E197" s="4" t="inlineStr">
+      <c r="F197" s="4" t="inlineStr">
         <is>
           <t>2084024529</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr"/>
-      <c r="G197" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="H197" s="4" t="inlineStr"/>
-      <c r="I197" s="4" t="inlineStr"/>
+      <c r="G197" s="4" t="n"/>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="n"/>
+      <c r="J197" s="4" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I197"/>
   <mergeCells count="16">
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A128:I128"/>
-    <mergeCell ref="A107:I107"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A160:I160"/>
-    <mergeCell ref="A96:I96"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A100:K100"/>
+    <mergeCell ref="A96:K96"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A128:K128"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A107:K107"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A160:K160"/>
+    <mergeCell ref="A90:K90"/>
+    <mergeCell ref="A118:K118"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7518,10 +7788,10 @@
           <t>【メンズ - クォーツ】</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -7878,10 +8148,10 @@
           <t>【メンズ - 機械式】</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -8077,10 +8347,10 @@
           <t>【レディース - クォーツ】</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -8299,10 +8569,10 @@
           <t>【レディース - 機械式】</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -8356,10 +8626,10 @@
           <t>【ユニセックス】</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -8436,10 +8706,10 @@
           <t>【特殊カテゴリ】</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr"/>

--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -8775,7 +8775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -8784,206 +8784,252 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>■ カテゴリ判定ロジック（4段階フォールバック）</t>
+          <t>■ カテゴリ判定ロジック（6段階フォールバック）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>優先度1: ブランド + シリーズ 完全一致 → そのcategory_idを採用</t>
+          <t>優先度0: ブランド + 型番 完全一致（最優先）→ そのcategory_idを採用</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  例: SEIKO + SPIRIT → 2084211407</t>
+          <t xml:space="preserve">  例: SEIKO + SBBN015 → 該当行のcategory_id</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr"/>
+      <c r="A5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>優先度2: ブランドのみ一致（シリーズ不明）→「（その他）」行のcategory_idを採用</t>
+          <t>優先度1: ブランド + シリーズ 完全一致 → そのcategory_idを採用</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  例: SEIKO + (不明シリーズ) → 2084053759</t>
+          <t xml:space="preserve">  例: SEIKO + SPIRIT → 2084211407</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ※ keywordsに登録された別名・略称でも一致判定される</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>優先度3: ブランド未登録 → Sheet2「汎用カテゴリ」から性別+ムーブメント+針数で検索</t>
-        </is>
-      </c>
+      <c r="A9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  例: 不明ブランド + メンズ + Quartz + 3針 → 2084223456</t>
+          <t>優先度1.5: シリーズ前方一致 → 先頭部分が一致するシリーズのcategory_idを採用</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  例: G-SHOCK FROGMAN → G-SHOCK のcategory_idにフォールバック</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>優先度4: 上記すべて該当なし → カテゴリ空白（手動入力）</t>
-        </is>
-      </c>
+      <c r="A12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr"/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>優先度2: ブランドのみ一致（シリーズ不明）→「（その他）」行のcategory_idを採用</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  例: SEIKO + (不明シリーズ) → 2084053759</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>■ Sheet1「ブランド別マッピング」の記入ルール</t>
-        </is>
-      </c>
+      <c r="A15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>優先度3: ブランド未登録 → Sheet2「汎用カテゴリ」から性別+ムーブメント+針数で検索</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>brand_en: ブランド英字（大文字推奨）。AIの認識結果と照合する主キー</t>
+          <t xml:space="preserve">  例: 不明ブランド + メンズ + Quartz + 3針 → 2084223456</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>brand_kana: ブランドのカタカナ表記。ヤフオクカテゴリ表の表記に合わせる</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>series_en: シリーズ英字。AIの認識結果と照合</t>
+          <t>優先度4: 上記すべて該当なし → カテゴリ空白（手動入力）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>series_kana: シリーズのカタカナ表記</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>category_id: ヤフオクカテゴリ番号</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>gender: 性別が固定のシリーズのみ記入（LUKIAはレディース等）</t>
+          <t>■ Sheet1「ブランド別マッピング」の記入ルール</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>type: 基本「本体」のみ。パーツ・ベルト等は不要</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>keywords: 英字の別名・略称。カンマ区切りで複数指定可</t>
+          <t>brand_en: ブランド英字（大文字推奨）。AIの認識結果と照合する主キー</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>notes: メモ欄（システムは参照しない）</t>
+          <t>brand_kana: ブランドのカタカナ表記。ヤフオクカテゴリ表の表記に合わせる</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>model_number: 型番。カンマ区切りで複数指定可。優先度0の照合に使用</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>★ 各ブランドに「（その他）」行を必ず1行追加すること（黄色行）</t>
+          <t>series_en: シリーズ英字。AIの認識結果と照合</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>★ 性別不明ブランド（DIESEL等）はcategory_id空欄にすること（ピンク行）</t>
+          <t>series_kana: シリーズのカタカナ表記</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>★ 行の追加・削除は自由。Excelを編集するだけでルール変更可能</t>
+          <t>category_id: ヤフオクカテゴリ番号</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr"/>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>gender: 性別が固定のシリーズのみ記入（LUKIAはレディース等）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr"/>
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>type: 基本「本体」のみ。パーツ・ベルト等は不要</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>■ Sheet2「汎用カテゴリ」の使い方</t>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>keywords: 英字の別名・略称。カンマ区切りで複数指定可。優先度1の照合に使用</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr"/>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>notes: メモ欄（システムは参照しない）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>ブランドがSheet1に未登録だった場合のフォールバック先</t>
+          <t>additional_word: 出品時にタイトル等へ追加する単語</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>性別（メンズ/レディース）+ ムーブメント + 針タイプで該当カテゴリを検索</t>
-        </is>
-      </c>
+      <c r="A35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>★ 各ブランドに「（その他）」行を必ず1行追加すること（黄色行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>★ 性別不明ブランド（DIESEL等）はcategory_id空欄にすること（ピンク行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>★ 行の追加・削除は自由。Excelを編集するだけでルール変更可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>■ Sheet2「汎用カテゴリ」の使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ブランドがSheet1に未登録だった場合のフォールバック先</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>性別（メンズ/レディース）+ ムーブメント + 針タイプで該当カテゴリを検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>基本的にこのシートの編集は不要（ヤフオクの既存カテゴリ体系のため）</t>
         </is>

--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -161,11 +161,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,6 +205,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,12 +575,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K197"/>
+  <dimension ref="A1:L197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -593,53 +604,59 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>brand_aliases
+（ブランド別名）</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>model_number
 （型番）</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>series_en
 （シリーズ英字）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>series_kana
 （シリーズカナ）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>category_id
 （カテゴリ番号）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gender
 （性別）</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>type
 （種別）</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>keywords
 （別名・キーワード）</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>notes
 （備考）</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>additional_word
 （追加単語）</t>
@@ -662,6 +679,7 @@
       <c r="I2" s="13" t="n"/>
       <c r="J2" s="13" t="n"/>
       <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -674,34 +692,35 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>GRAND SEIKO</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>グランドセイコー</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>2084053754</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -714,30 +733,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>DOLCE</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>ドルチェ</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>2084053755</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -750,30 +770,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>EXCELINE</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>エクセリーヌ</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>2084053756</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -786,38 +807,39 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>LUKIA</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>ルキア</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>2084053757</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
           <t>LK</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -830,30 +852,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>BRIGHTZ</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>ブライツ</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>2084053758</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -866,30 +889,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>CREDOR</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>クレドール</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>2084054005</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -902,34 +926,35 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>SPIRIT</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>スピリット</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>2084211407</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>SPILIT</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>※ヤフオク表記「SPILIT」</t>
         </is>
@@ -946,30 +971,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>WIRED</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>ワイアード</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>2084211408</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -982,30 +1008,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>PROSPEX</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>プロスペックス</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>2084211409</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1018,30 +1045,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>IGNITION</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>イグニッション</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>2084211410</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1054,30 +1082,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>ALBA</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>アルバ</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>2084217133</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1090,30 +1119,31 @@
           <t>セイコー</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>2084053759</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -1135,6 +1165,7 @@
       <c r="I15" s="13" t="n"/>
       <c r="J15" s="13" t="n"/>
       <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1147,30 +1178,31 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ATTESA</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>アテッサ</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>2084209455</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1183,38 +1215,39 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>WICCA</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>ウィッカ</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>2084209458</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
           <t>Wicca</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1227,30 +1260,31 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>EXCEED</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>エクシード</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>2084209454</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1263,30 +1297,31 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Q&amp;Q</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>キューアンドキュー</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>2084314563</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1299,34 +1334,35 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>クロスシー</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>2084209457</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="n"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1339,30 +1375,31 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>PROMASTER</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>プロマスター</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>2084209456</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1375,30 +1412,31 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>REGUNO</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>レグノ</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>2084314562</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1411,30 +1449,31 @@
           <t>シチズン</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>2084209459</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -1456,6 +1495,7 @@
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="13" t="n"/>
       <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1468,34 +1508,35 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>PRO TREK</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>プロトレック</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>2084032116</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
           <t>PROTREK</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1508,30 +1549,31 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>OCEANUS</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>オシアナス</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>2084211406</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1544,30 +1586,31 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>EDIFICE</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>エディフィス</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>2084310827</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1580,30 +1623,31 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>DATA BANK</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>データバンク</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>2084226882</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1616,30 +1660,31 @@
           <t>カシオ</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>2084032138</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -1661,6 +1706,7 @@
       <c r="I30" s="13" t="n"/>
       <c r="J30" s="13" t="n"/>
       <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1673,30 +1719,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>GIEZ</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>ジーズ</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>2084041606</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1709,30 +1756,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>MR-G</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>MR-G</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>2084041607</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1745,30 +1793,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>MT-G</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>MT-G</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>2084041608</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1781,30 +1830,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>FROGMAN</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>フロッグマン</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>2084045111</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1817,30 +1867,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>MUDMAN</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>マッドマン</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>2084045108</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1853,30 +1904,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>GULFMAN</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>ガルフマン</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>2084045119</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1889,30 +1941,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>RISEMAN</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>ライズマン</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>2084045109</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1925,30 +1978,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>TOUGH SOLAR</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>タフソーラー</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>2084207807</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1961,30 +2015,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>G-LIDE</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Gライド</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>2084262304</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1997,30 +2052,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Crazy Colors</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>クレイジーカラーズ</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>2084262305</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2033,30 +2089,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>コラボレーションモデル</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>コラボレーションモデル</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>2084262308</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2069,30 +2126,31 @@
           <t>G-SHOCK</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>2084041610</t>
         </is>
       </c>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="6" t="inlineStr">
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -2114,6 +2172,7 @@
       <c r="I43" s="13" t="n"/>
       <c r="J43" s="13" t="n"/>
       <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2126,34 +2185,35 @@
           <t>Baby-G</t>
         </is>
       </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Tripper</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>トリッパー</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>2084209445</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="n"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2166,34 +2226,35 @@
           <t>Baby-G</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Reef</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>リーフ</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>2084209446</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="n"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2206,34 +2267,35 @@
           <t>Baby-G</t>
         </is>
       </c>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>2084209449</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="n"/>
-      <c r="J46" s="6" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -2255,6 +2317,7 @@
       <c r="I47" s="13" t="n"/>
       <c r="J47" s="13" t="n"/>
       <c r="K47" s="14" t="n"/>
+      <c r="L47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2267,34 +2330,35 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>CONSTELLATION</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>コンステレーション</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>2084053736</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
           <t>Constellation</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2307,34 +2371,35 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>DE VILLE</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>デビル</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>2084053739</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
           <t>De Ville, DeVille</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2347,34 +2412,35 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER AQUA TERRA</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>シーマスター アクアテラ</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>2084221466</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
           <t>Aqua Terra</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2387,34 +2453,35 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER PLANET OCEAN</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>シーマスター プラネットオーシャン</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>2084221467</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
           <t>Planet Ocean</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2427,30 +2494,31 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER 300M</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>シーマスター 300M</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>2084221468</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2463,30 +2531,31 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>SEAMASTER</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>シーマスター</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>2084221469</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>★シーマスター系フォールバック</t>
         </is>
@@ -2503,30 +2572,31 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>SPEEDMASTER DATE</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>スピードマスター デイト</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>2084221470</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2539,34 +2609,35 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>SPEEDMASTER PROFESSIONAL</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>スピードマスター プロフェッショナル</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>2084221471</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
           <t>Pro, Moonwatch</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -2579,30 +2650,31 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>SPEEDMASTER</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>スピードマスター</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>2084221472</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>★スピマス系フォールバック</t>
         </is>
@@ -2619,30 +2691,31 @@
           <t>オメガ</t>
         </is>
       </c>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>2084053740</t>
         </is>
       </c>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="n"/>
-      <c r="J57" s="6" t="inlineStr">
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -2664,6 +2737,7 @@
       <c r="I58" s="13" t="n"/>
       <c r="J58" s="13" t="n"/>
       <c r="K58" s="14" t="n"/>
+      <c r="L58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2676,34 +2750,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>GMT MASTER</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>GMTマスター</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>2084310776</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
           <t>GMT-Master, GMT Master II</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2716,34 +2791,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>AIR-KING</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>エアキング</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>2084310778</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
           <t>Air King, Air-King</t>
         </is>
       </c>
-      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2756,34 +2832,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>EXPLORER I</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>エクスプローラーI</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>2084310780</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
           <t>Explorer 1</t>
         </is>
       </c>
-      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -2796,34 +2873,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>EXPLORER II</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>エクスプローラーII</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>2084310782</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
           <t>Explorer 2</t>
         </is>
       </c>
-      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2836,30 +2914,31 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>SUBMARINER</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>サブマリーナ</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>2084310784</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -2872,34 +2951,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>SEA-DWELLER</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>シードゥエラー</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>2084310786</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
           <t>Sea Dweller</t>
         </is>
       </c>
-      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2912,30 +2992,31 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>CELLINI</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>チェリーニ</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>2084024501</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2948,34 +3029,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="C66" s="17" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>DAY-DATE</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>デイデイト</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>2084310788</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
           <t>Day Date, Daydate</t>
         </is>
       </c>
-      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2988,34 +3070,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="C67" s="17" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>DATEJUST</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>デイトジャスト</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>2084310792</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>メンズ</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="inlineStr">
         <is>
           <t>※男性用</t>
         </is>
@@ -3032,34 +3115,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="C68" s="17" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>DATEJUST</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>デイトジャスト</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>2084310790</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>レディース</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>※女性用</t>
         </is>
@@ -3076,34 +3160,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="C69" s="17" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>DAYTONA</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>デイトナ</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>2084310794</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
           <t>Cosmograph Daytona</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -3116,30 +3201,31 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="C70" s="17" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>MILGAUSS</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>ミルガウス</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>2084024500</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J70" s="4" t="n"/>
+      <c r="K70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -3152,34 +3238,35 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>YACHT-MASTER</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>ヨットマスター</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>2084024498</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
           <t>Yacht Master, Yachtmaster</t>
         </is>
       </c>
-      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -3192,30 +3279,31 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>CAMELEON</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>カメレオン</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>2084024502</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3228,30 +3316,31 @@
           <t>ロレックス</t>
         </is>
       </c>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="C73" s="17" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>2084024489</t>
         </is>
       </c>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="n"/>
-      <c r="J73" s="6" t="inlineStr">
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3273,6 +3362,7 @@
       <c r="I74" s="13" t="n"/>
       <c r="J74" s="13" t="n"/>
       <c r="K74" s="14" t="n"/>
+      <c r="L74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -3285,30 +3375,31 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="C75" s="17" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>AQUATIMER</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>アクアタイマー</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>2084303663</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -3321,34 +3412,35 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="C76" s="17" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>INGENIEUR</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>インヂュニア</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>2084303664</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
           <t>Ingenieur</t>
         </is>
       </c>
-      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3361,34 +3453,35 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="C77" s="17" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>DA VINCI</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>ダ・ヴィンチ</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>2084303666</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
           <t>Da Vinci</t>
         </is>
       </c>
-      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -3401,34 +3494,35 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="C78" s="17" t="n"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>PILOT WATCH</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>パイロット・ウォッチ</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>2084303667</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
           <t>Pilot, Flieger</t>
         </is>
       </c>
-      <c r="J78" s="4" t="n"/>
+      <c r="K78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3441,30 +3535,31 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="C79" s="17" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>PORTOFINO</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>ポートフィノ</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>2084303668</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -3477,34 +3572,35 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="C80" s="17" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>PORTUGIESER</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>ポルトギーゼ</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>2084303669</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
           <t>Portuguese</t>
         </is>
       </c>
-      <c r="J80" s="4" t="n"/>
+      <c r="K80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -3517,30 +3613,31 @@
           <t>IWC</t>
         </is>
       </c>
-      <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="C81" s="17" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>2084303695</t>
         </is>
       </c>
-      <c r="G81" s="6" t="n"/>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="n"/>
-      <c r="J81" s="6" t="inlineStr">
+      <c r="H81" s="6" t="n"/>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="n"/>
+      <c r="K81" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3562,6 +3659,7 @@
       <c r="I82" s="13" t="n"/>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="14" t="n"/>
+      <c r="L82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -3574,30 +3672,31 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C83" s="4" t="n"/>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="C83" s="17" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>AQUARACER</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>アクアレーサー</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>2084262302</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -3610,30 +3709,31 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="C84" s="17" t="n"/>
+      <c r="D84" s="4" t="n"/>
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>CARRERA</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>カレラ</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>2084221480</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="n"/>
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J84" s="4" t="n"/>
+      <c r="K84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -3646,34 +3746,35 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C85" s="4" t="n"/>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="C85" s="17" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>FORMULA 1</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>フォーミュラ</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>2084262301</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n"/>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H85" s="4" t="n"/>
       <c r="I85" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
           <t>Formula, F1</t>
         </is>
       </c>
-      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -3686,30 +3787,31 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="C86" s="17" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>MONACO</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>モナコ</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>2084221479</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="n"/>
+      <c r="H86" s="4" t="n"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J86" s="4" t="n"/>
+      <c r="K86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -3722,30 +3824,31 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="C87" s="17" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>LINK</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>リンク</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>2084221481</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n"/>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="n"/>
+      <c r="H87" s="4" t="n"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J87" s="4" t="n"/>
+      <c r="K87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -3758,30 +3861,31 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C88" s="4" t="n"/>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="C88" s="17" t="n"/>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>2000 SERIES</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>2000シリーズ</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>2084262303</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="n"/>
+      <c r="H88" s="4" t="n"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J88" s="4" t="n"/>
+      <c r="K88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -3794,30 +3898,31 @@
           <t>タグ・ホイヤー</t>
         </is>
       </c>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="C89" s="17" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>2084221482</t>
         </is>
       </c>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="n"/>
-      <c r="J89" s="6" t="inlineStr">
+      <c r="H89" s="6" t="n"/>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="n"/>
+      <c r="K89" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -3839,6 +3944,7 @@
       <c r="I90" s="13" t="n"/>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="14" t="n"/>
+      <c r="L90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -3851,30 +3957,31 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="C91" s="17" t="n"/>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>KHAKI</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>カーキ</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t>2084221485</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="n"/>
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J91" s="4" t="n"/>
+      <c r="K91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -3887,30 +3994,31 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>JAZZMASTER</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>ジャズマスター</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>2084221487</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J92" s="4" t="n"/>
+      <c r="K92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3923,30 +4031,31 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="C93" s="17" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>VENTURA</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>ベンチュラ</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>2084221486</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -3959,30 +4068,31 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C94" s="4" t="n"/>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>LLOYD</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>ロイド</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr">
         <is>
           <t>2084221488</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n"/>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -3995,30 +4105,31 @@
           <t>ハミルトン</t>
         </is>
       </c>
-      <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="C95" s="17" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>2084221489</t>
         </is>
       </c>
-      <c r="G95" s="6" t="n"/>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I95" s="6" t="n"/>
-      <c r="J95" s="6" t="inlineStr">
+      <c r="H95" s="6" t="n"/>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="n"/>
+      <c r="K95" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -4040,6 +4151,7 @@
       <c r="I96" s="13" t="n"/>
       <c r="J96" s="13" t="n"/>
       <c r="K96" s="14" t="n"/>
+      <c r="L96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -4052,30 +4164,31 @@
           <t>オリエント</t>
         </is>
       </c>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="C97" s="17" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>ORIENT STAR</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>オリエントスター</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>2084211535</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -4088,30 +4201,31 @@
           <t>オリエント</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="C98" s="17" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>KING MASTER</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>キングマスター</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>2084211536</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J98" s="4" t="n"/>
+      <c r="K98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -4124,30 +4238,31 @@
           <t>オリエント</t>
         </is>
       </c>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="C99" s="17" t="n"/>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>2084211537</t>
         </is>
       </c>
-      <c r="G99" s="6" t="n"/>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="n"/>
-      <c r="J99" s="6" t="inlineStr">
+      <c r="H99" s="6" t="n"/>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="n"/>
+      <c r="K99" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -4169,6 +4284,7 @@
       <c r="I100" s="13" t="n"/>
       <c r="J100" s="13" t="n"/>
       <c r="K100" s="14" t="n"/>
+      <c r="L100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -4181,30 +4297,31 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C101" s="4" t="n"/>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="C101" s="17" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>ADMIRAL</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>アドミラル</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>2084308400</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n"/>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J101" s="4" t="n"/>
+      <c r="K101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -4217,30 +4334,31 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="C102" s="17" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>GRAND CLASSIC</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>グランドクラシック</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>2084308401</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -4253,30 +4371,31 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C103" s="4" t="n"/>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="C103" s="17" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>CONQUEST</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>コンクエスト</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>2084308402</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n"/>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -4289,30 +4408,31 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C104" s="4" t="n"/>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="C104" s="17" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>DOLCE VITA</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>ドルチェビータ</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>2084308403</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n"/>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -4325,34 +4445,35 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C105" s="4" t="n"/>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="C105" s="17" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>HYDROCONQUEST</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>ハイドロ コンクエスト</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>2084308404</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n"/>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H105" s="4" t="n"/>
       <c r="I105" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
           <t>Hydro Conquest</t>
         </is>
       </c>
-      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -4365,30 +4486,31 @@
           <t>ロンジン</t>
         </is>
       </c>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="C106" s="17" t="n"/>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
+      <c r="G106" s="6" t="inlineStr">
         <is>
           <t>2084308405</t>
         </is>
       </c>
-      <c r="G106" s="6" t="n"/>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I106" s="6" t="n"/>
-      <c r="J106" s="6" t="inlineStr">
+      <c r="H106" s="6" t="n"/>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="n"/>
+      <c r="K106" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -4410,6 +4532,7 @@
       <c r="I107" s="13" t="n"/>
       <c r="J107" s="13" t="n"/>
       <c r="K107" s="14" t="n"/>
+      <c r="L107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -4422,34 +4545,35 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C108" s="4" t="n"/>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="C108" s="17" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>SANTOS</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>サントス</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="G108" s="4" t="inlineStr">
         <is>
           <t>2084053718</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n"/>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H108" s="4" t="n"/>
       <c r="I108" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
           <t>Santos de Cartier</t>
         </is>
       </c>
-      <c r="J108" s="4" t="n"/>
+      <c r="K108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -4462,34 +4586,35 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="C109" s="17" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>PANTHERE</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>パンテール</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>2084053720</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n"/>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H109" s="4" t="n"/>
       <c r="I109" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
           <t>Panthere de Cartier</t>
         </is>
       </c>
-      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -4502,30 +4627,31 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C110" s="4" t="n"/>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="C110" s="17" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>BAIGNOIRE</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>ベニュワール</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>2084053721</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n"/>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="n"/>
+      <c r="H110" s="4" t="n"/>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J110" s="4" t="n"/>
+      <c r="K110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -4538,30 +4664,31 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C111" s="4" t="n"/>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="C111" s="17" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>RANIERE</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>ラニエール</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t>2084053722</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n"/>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J111" s="4" t="n"/>
+      <c r="K111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -4574,30 +4701,31 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C112" s="4" t="n"/>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="C112" s="17" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>ROADSTER</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
+      <c r="F112" s="4" t="inlineStr">
         <is>
           <t>ロードスター</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="G112" s="4" t="inlineStr">
         <is>
           <t>2084053719</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n"/>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -4610,34 +4738,35 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="C113" s="17" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>TANK FRANCAISE</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>タンクフランセーズ</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>2084053728</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H113" s="4" t="n"/>
       <c r="I113" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
           <t>Tank Française</t>
         </is>
       </c>
-      <c r="J113" s="4" t="n"/>
+      <c r="K113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -4650,34 +4779,35 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="C114" s="17" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>TANK AMERICAINE</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>タンクアメリカン</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="G114" s="4" t="inlineStr">
         <is>
           <t>2084053729</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n"/>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H114" s="4" t="n"/>
       <c r="I114" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
           <t>Tank American</t>
         </is>
       </c>
-      <c r="J114" s="4" t="n"/>
+      <c r="K114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -4690,30 +4820,31 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C115" s="4" t="n"/>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="C115" s="17" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>MUST TANK</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>マストタンク</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="G115" s="4" t="inlineStr">
         <is>
           <t>2084053730</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n"/>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J115" s="4" t="n"/>
+      <c r="K115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -4726,34 +4857,35 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C116" s="4" t="n"/>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="C116" s="17" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>PASHA</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>パシャ</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="G116" s="4" t="inlineStr">
         <is>
           <t>2084053724</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n"/>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H116" s="4" t="n"/>
       <c r="I116" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
           <t>Pasha C, Pasha de Cartier</t>
         </is>
       </c>
-      <c r="J116" s="4" t="n"/>
+      <c r="K116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -4766,30 +4898,31 @@
           <t>カルティエ</t>
         </is>
       </c>
-      <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="C117" s="17" t="n"/>
+      <c r="D117" s="6" t="n"/>
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr">
+      <c r="G117" s="6" t="inlineStr">
         <is>
           <t>2084053723</t>
         </is>
       </c>
-      <c r="G117" s="6" t="n"/>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I117" s="6" t="n"/>
-      <c r="J117" s="6" t="inlineStr">
+      <c r="H117" s="6" t="n"/>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="n"/>
+      <c r="K117" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -4811,6 +4944,7 @@
       <c r="I118" s="13" t="n"/>
       <c r="J118" s="13" t="n"/>
       <c r="K118" s="14" t="n"/>
+      <c r="L118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -4823,30 +4957,31 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C119" s="4" t="n"/>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="C119" s="17" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>ASSIOMA</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>アショーマ</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="G119" s="4" t="inlineStr">
         <is>
           <t>2084285566</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n"/>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J119" s="4" t="n"/>
+      <c r="K119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -4859,34 +4994,35 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C120" s="4" t="n"/>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="C120" s="17" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>ALUMINIUM</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>アルミニウム</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="G120" s="4" t="inlineStr">
         <is>
           <t>2084053746</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H120" s="4" t="n"/>
       <c r="I120" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
           <t>Aluminum</t>
         </is>
       </c>
-      <c r="J120" s="4" t="n"/>
+      <c r="K120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -4899,30 +5035,31 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C121" s="4" t="n"/>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="C121" s="17" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>ERGON</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>エルゴン</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="G121" s="4" t="inlineStr">
         <is>
           <t>2084285567</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n"/>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -4935,30 +5072,31 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C122" s="4" t="n"/>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="C122" s="17" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="4" t="inlineStr">
         <is>
           <t>DIAGONO</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>ディアゴノ</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="G122" s="4" t="inlineStr">
         <is>
           <t>2084053749</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J122" s="4" t="n"/>
+      <c r="K122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -4971,34 +5109,35 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C123" s="4" t="n"/>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="C123" s="17" t="n"/>
+      <c r="D123" s="4" t="n"/>
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>B.ZERO1</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>ビーゼロワン</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr">
+      <c r="G123" s="4" t="inlineStr">
         <is>
           <t>2084053747</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n"/>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H123" s="4" t="n"/>
       <c r="I123" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
           <t>B-Zero1, BZero1</t>
         </is>
       </c>
-      <c r="J123" s="4" t="n"/>
+      <c r="K123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -5011,34 +5150,35 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C124" s="4" t="n"/>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="C124" s="17" t="n"/>
+      <c r="D124" s="4" t="n"/>
+      <c r="E124" s="4" t="inlineStr">
         <is>
           <t>BVLGARI BVLGARI</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>ブルガリブルガリ</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
+      <c r="G124" s="4" t="inlineStr">
         <is>
           <t>2084053748</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n"/>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H124" s="4" t="n"/>
       <c r="I124" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="J124" s="4" t="n"/>
+      <c r="K124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -5051,30 +5191,31 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C125" s="4" t="n"/>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="C125" s="17" t="n"/>
+      <c r="D125" s="4" t="n"/>
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>SOLOTEMPO</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>ソロテンポ</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>2084053752</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n"/>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="n"/>
+      <c r="H125" s="4" t="n"/>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J125" s="4" t="n"/>
+      <c r="K125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -5087,30 +5228,31 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C126" s="4" t="n"/>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="C126" s="17" t="n"/>
+      <c r="D126" s="4" t="n"/>
+      <c r="E126" s="4" t="inlineStr">
         <is>
           <t>RETTANGOLO</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>レッタンゴロ</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
+      <c r="G126" s="4" t="inlineStr">
         <is>
           <t>2084053751</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n"/>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="n"/>
+      <c r="H126" s="4" t="n"/>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J126" s="4" t="n"/>
+      <c r="K126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -5123,30 +5265,31 @@
           <t>ブルガリ</t>
         </is>
       </c>
-      <c r="C127" s="6" t="n"/>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="C127" s="17" t="n"/>
+      <c r="D127" s="6" t="n"/>
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
+      <c r="G127" s="6" t="inlineStr">
         <is>
           <t>2084053753</t>
         </is>
       </c>
-      <c r="G127" s="6" t="n"/>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I127" s="6" t="n"/>
-      <c r="J127" s="6" t="inlineStr">
+      <c r="H127" s="6" t="n"/>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="n"/>
+      <c r="K127" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5168,6 +5311,7 @@
       <c r="I128" s="13" t="n"/>
       <c r="J128" s="13" t="n"/>
       <c r="K128" s="14" t="n"/>
+      <c r="L128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
@@ -5180,18 +5324,19 @@
           <t>ディーゼル</t>
         </is>
       </c>
-      <c r="C129" s="8" t="n"/>
+      <c r="C129" s="17" t="n"/>
       <c r="D129" s="8" t="n"/>
       <c r="E129" s="8" t="n"/>
       <c r="F129" s="8" t="n"/>
       <c r="G129" s="8" t="n"/>
-      <c r="H129" s="8" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I129" s="8" t="n"/>
-      <c r="J129" s="8" t="inlineStr">
+      <c r="H129" s="8" t="n"/>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J129" s="8" t="n"/>
+      <c r="K129" s="8" t="inlineStr">
         <is>
           <t>★性別不明→空白（Q1）</t>
         </is>
@@ -5208,18 +5353,19 @@
           <t>グッチ</t>
         </is>
       </c>
-      <c r="C130" s="8" t="n"/>
+      <c r="C130" s="17" t="n"/>
       <c r="D130" s="8" t="n"/>
       <c r="E130" s="8" t="n"/>
       <c r="F130" s="8" t="n"/>
       <c r="G130" s="8" t="n"/>
-      <c r="H130" s="8" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I130" s="8" t="n"/>
-      <c r="J130" s="8" t="inlineStr">
+      <c r="H130" s="8" t="n"/>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J130" s="8" t="n"/>
+      <c r="K130" s="8" t="inlineStr">
         <is>
           <t>★性別不明→空白（Q1）</t>
         </is>
@@ -5236,30 +5382,31 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C131" s="4" t="n"/>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="C131" s="17" t="n"/>
+      <c r="D131" s="4" t="n"/>
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>H WATCH</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>Hウォッチ</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>2084209450</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n"/>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J131" s="4" t="n"/>
+      <c r="K131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -5272,30 +5419,31 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C132" s="4" t="n"/>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="C132" s="17" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>CLIPPER</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>クリッパー</t>
         </is>
       </c>
-      <c r="F132" s="4" t="inlineStr">
+      <c r="G132" s="4" t="inlineStr">
         <is>
           <t>2084209451</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n"/>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="n"/>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J132" s="4" t="n"/>
+      <c r="K132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -5308,30 +5456,31 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C133" s="4" t="n"/>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="C133" s="17" t="n"/>
+      <c r="D133" s="4" t="n"/>
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t>KELLY</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="F133" s="4" t="inlineStr">
         <is>
           <t>ケリー</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="G133" s="4" t="inlineStr">
         <is>
           <t>2084209452</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n"/>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="n"/>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J133" s="4" t="n"/>
+      <c r="K133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -5344,30 +5493,31 @@
           <t>エルメス</t>
         </is>
       </c>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="C134" s="17" t="n"/>
+      <c r="D134" s="6" t="n"/>
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
+      <c r="G134" s="6" t="inlineStr">
         <is>
           <t>2084209453</t>
         </is>
       </c>
-      <c r="G134" s="6" t="n"/>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I134" s="6" t="n"/>
-      <c r="J134" s="6" t="inlineStr">
+      <c r="H134" s="6" t="n"/>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="n"/>
+      <c r="K134" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5384,30 +5534,31 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C135" s="4" t="n"/>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="C135" s="17" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="4" t="inlineStr">
         <is>
           <t>NAVITIMER</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>ナビタイマー</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr">
+      <c r="G135" s="4" t="inlineStr">
         <is>
           <t>2084221499</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n"/>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J135" s="4" t="n"/>
+      <c r="K135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -5420,34 +5571,35 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C136" s="4" t="n"/>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="C136" s="17" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>CHRONOMAT</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>クロノマット</t>
         </is>
       </c>
-      <c r="F136" s="4" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t>2084221495</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H136" s="4" t="n"/>
       <c r="I136" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
           <t>Chronomat Evolution</t>
         </is>
       </c>
-      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -5460,34 +5612,35 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="C137" s="17" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="inlineStr">
         <is>
           <t>SUPEROCEAN</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>スーパーオーシャン</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr">
+      <c r="G137" s="4" t="inlineStr">
         <is>
           <t>2084221497</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H137" s="4" t="n"/>
       <c r="I137" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
           <t>Super Ocean</t>
         </is>
       </c>
-      <c r="J137" s="4" t="n"/>
+      <c r="K137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -5500,30 +5653,31 @@
           <t>ブライトリング</t>
         </is>
       </c>
-      <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="C138" s="17" t="n"/>
+      <c r="D138" s="6" t="n"/>
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
+      <c r="G138" s="6" t="inlineStr">
         <is>
           <t>2084221494</t>
         </is>
       </c>
-      <c r="G138" s="6" t="n"/>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I138" s="6" t="n"/>
-      <c r="J138" s="6" t="inlineStr">
+      <c r="H138" s="6" t="n"/>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="n"/>
+      <c r="K138" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5540,30 +5694,31 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C139" s="4" t="n"/>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="C139" s="17" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>CASABLANCA</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="F139" s="4" t="inlineStr">
         <is>
           <t>カサブランカ</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="G139" s="4" t="inlineStr">
         <is>
           <t>2084053743</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n"/>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="n"/>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J139" s="4" t="n"/>
+      <c r="K139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -5576,30 +5731,31 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C140" s="4" t="n"/>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="C140" s="17" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>CONQUISTADOR</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>コンキスタドール</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="G140" s="4" t="inlineStr">
         <is>
           <t>2084053741</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n"/>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I140" s="4" t="n"/>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J140" s="4" t="n"/>
+      <c r="K140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -5612,30 +5768,31 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C141" s="4" t="n"/>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="C141" s="17" t="n"/>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="4" t="inlineStr">
         <is>
           <t>LONG ISLAND</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>ロングアイランド</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="G141" s="4" t="inlineStr">
         <is>
           <t>2084053742</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n"/>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="n"/>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J141" s="4" t="n"/>
+      <c r="K141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -5648,30 +5805,31 @@
           <t>フランク・ミュラー</t>
         </is>
       </c>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="C142" s="17" t="n"/>
+      <c r="D142" s="6" t="n"/>
+      <c r="E142" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr">
+      <c r="G142" s="6" t="inlineStr">
         <is>
           <t>2084053745</t>
         </is>
       </c>
-      <c r="G142" s="6" t="n"/>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I142" s="6" t="n"/>
-      <c r="J142" s="6" t="inlineStr">
+      <c r="H142" s="6" t="n"/>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="n"/>
+      <c r="K142" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5688,30 +5846,31 @@
           <t>チュードル</t>
         </is>
       </c>
-      <c r="C143" s="4" t="n"/>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="C143" s="17" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="inlineStr">
         <is>
           <t>SUBMARINER</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>サブマリーナ</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="G143" s="4" t="inlineStr">
         <is>
           <t>2084303672</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n"/>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J143" s="4" t="n"/>
+      <c r="K143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -5724,30 +5883,31 @@
           <t>チュードル</t>
         </is>
       </c>
-      <c r="C144" s="4" t="n"/>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="C144" s="17" t="n"/>
+      <c r="D144" s="4" t="n"/>
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>RANGER</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>レンジャー</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="G144" s="4" t="inlineStr">
         <is>
           <t>2084303674</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n"/>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="n"/>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J144" s="4" t="n"/>
+      <c r="K144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -5760,30 +5920,31 @@
           <t>チュードル</t>
         </is>
       </c>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="C145" s="17" t="n"/>
+      <c r="D145" s="6" t="n"/>
+      <c r="E145" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr">
+      <c r="G145" s="6" t="inlineStr">
         <is>
           <t>2084303675</t>
         </is>
       </c>
-      <c r="G145" s="6" t="n"/>
-      <c r="H145" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I145" s="6" t="n"/>
-      <c r="J145" s="6" t="inlineStr">
+      <c r="H145" s="6" t="n"/>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="n"/>
+      <c r="K145" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5800,30 +5961,31 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C146" s="4" t="n"/>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="C146" s="17" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>LUMINOR BASE</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>ルミノール ベース</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="G146" s="4" t="inlineStr">
         <is>
           <t>2084221473</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n"/>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J146" s="4" t="n"/>
+      <c r="K146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -5836,30 +5998,31 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C147" s="4" t="n"/>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="C147" s="17" t="n"/>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="4" t="inlineStr">
         <is>
           <t>LUMINOR MARINA</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>ルミノール マリーナ</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="G147" s="4" t="inlineStr">
         <is>
           <t>2084221474</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n"/>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I147" s="4" t="n"/>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J147" s="4" t="n"/>
+      <c r="K147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -5872,30 +6035,31 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n"/>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="C148" s="17" t="n"/>
+      <c r="D148" s="4" t="n"/>
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>RADIOMIR</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>ラジオミール</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr">
+      <c r="G148" s="4" t="inlineStr">
         <is>
           <t>2084221475</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n"/>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="n"/>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J148" s="4" t="n"/>
+      <c r="K148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -5908,30 +6072,31 @@
           <t>オフィチーネ パネライ</t>
         </is>
       </c>
-      <c r="C149" s="6" t="n"/>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="C149" s="17" t="n"/>
+      <c r="D149" s="6" t="n"/>
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr">
+      <c r="G149" s="6" t="inlineStr">
         <is>
           <t>2084221476</t>
         </is>
       </c>
-      <c r="G149" s="6" t="n"/>
-      <c r="H149" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I149" s="6" t="n"/>
-      <c r="J149" s="6" t="inlineStr">
+      <c r="H149" s="6" t="n"/>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="n"/>
+      <c r="K149" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -5948,30 +6113,31 @@
           <t>シャネル</t>
         </is>
       </c>
-      <c r="C150" s="4" t="n"/>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="C150" s="17" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>J12</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
+      <c r="F150" s="4" t="inlineStr">
         <is>
           <t>J12</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr">
+      <c r="G150" s="4" t="inlineStr">
         <is>
           <t>2084308389</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n"/>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="n"/>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J150" s="4" t="n"/>
+      <c r="K150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -5984,30 +6150,31 @@
           <t>シャネル</t>
         </is>
       </c>
-      <c r="C151" s="4" t="n"/>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="C151" s="17" t="n"/>
+      <c r="D151" s="4" t="n"/>
+      <c r="E151" s="4" t="inlineStr">
         <is>
           <t>PREMIERE</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="F151" s="4" t="inlineStr">
         <is>
           <t>プルミエール</t>
         </is>
       </c>
-      <c r="F151" s="4" t="inlineStr">
+      <c r="G151" s="4" t="inlineStr">
         <is>
           <t>2084308390</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n"/>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I151" s="4" t="n"/>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J151" s="4" t="n"/>
+      <c r="K151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -6020,30 +6187,31 @@
           <t>シャネル</t>
         </is>
       </c>
-      <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="C152" s="17" t="n"/>
+      <c r="D152" s="6" t="n"/>
+      <c r="E152" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
+      <c r="G152" s="6" t="inlineStr">
         <is>
           <t>2084308394</t>
         </is>
       </c>
-      <c r="G152" s="6" t="n"/>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I152" s="6" t="n"/>
-      <c r="J152" s="6" t="inlineStr">
+      <c r="H152" s="6" t="n"/>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="n"/>
+      <c r="K152" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -6060,30 +6228,31 @@
           <t>ルミノックス</t>
         </is>
       </c>
-      <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="C153" s="17" t="n"/>
+      <c r="D153" s="6" t="n"/>
+      <c r="E153" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
+      <c r="G153" s="6" t="inlineStr">
         <is>
           <t>2084221504</t>
         </is>
       </c>
-      <c r="G153" s="6" t="n"/>
-      <c r="H153" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I153" s="6" t="n"/>
-      <c r="J153" s="6" t="inlineStr">
+      <c r="H153" s="6" t="n"/>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="n"/>
+      <c r="K153" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -6100,30 +6269,31 @@
           <t>ニクソン</t>
         </is>
       </c>
-      <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="C154" s="17" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
+      <c r="G154" s="6" t="inlineStr">
         <is>
           <t>2084308399</t>
         </is>
       </c>
-      <c r="G154" s="6" t="n"/>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I154" s="6" t="n"/>
-      <c r="J154" s="6" t="inlineStr">
+      <c r="H154" s="6" t="n"/>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="n"/>
+      <c r="K154" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -6140,34 +6310,35 @@
           <t>ガガミラノ</t>
         </is>
       </c>
-      <c r="C155" s="4" t="n"/>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="C155" s="17" t="n"/>
+      <c r="D155" s="4" t="n"/>
+      <c r="E155" s="4" t="inlineStr">
         <is>
           <t>MANUALE</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
+      <c r="F155" s="4" t="inlineStr">
         <is>
           <t>マニュアーレ</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr">
+      <c r="G155" s="4" t="inlineStr">
         <is>
           <t>2084303679</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n"/>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H155" s="4" t="n"/>
       <c r="I155" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
           <t>GaGa MILANO</t>
         </is>
       </c>
-      <c r="J155" s="4" t="n"/>
+      <c r="K155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -6180,34 +6351,35 @@
           <t>ガガミラノ</t>
         </is>
       </c>
-      <c r="C156" s="6" t="n"/>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="C156" s="17" t="n"/>
+      <c r="D156" s="6" t="n"/>
+      <c r="E156" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr">
+      <c r="G156" s="6" t="inlineStr">
         <is>
           <t>2084303681</t>
         </is>
       </c>
-      <c r="G156" s="6" t="n"/>
-      <c r="H156" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H156" s="6" t="n"/>
       <c r="I156" s="6" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr">
+        <is>
           <t>GaGa MILANO</t>
         </is>
       </c>
-      <c r="J156" s="6" t="inlineStr">
+      <c r="K156" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -6224,30 +6396,31 @@
           <t>スウォッチ</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n"/>
-      <c r="D157" s="4" t="inlineStr">
+      <c r="C157" s="17" t="n"/>
+      <c r="D157" s="4" t="n"/>
+      <c r="E157" s="4" t="inlineStr">
         <is>
           <t>CHRONO</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
+      <c r="F157" s="4" t="inlineStr">
         <is>
           <t>クロノ</t>
         </is>
       </c>
-      <c r="F157" s="4" t="inlineStr">
+      <c r="G157" s="4" t="inlineStr">
         <is>
           <t>2084024477</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n"/>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="n"/>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J157" s="4" t="n"/>
+      <c r="K157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -6260,30 +6433,31 @@
           <t>スウォッチ</t>
         </is>
       </c>
-      <c r="C158" s="4" t="n"/>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="C158" s="17" t="n"/>
+      <c r="D158" s="4" t="n"/>
+      <c r="E158" s="4" t="inlineStr">
         <is>
           <t>IRONY</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>アイロニー</t>
         </is>
       </c>
-      <c r="F158" s="4" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr">
         <is>
           <t>2084024486</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n"/>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I158" s="4" t="n"/>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J158" s="4" t="n"/>
+      <c r="K158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -6296,30 +6470,31 @@
           <t>スウォッチ</t>
         </is>
       </c>
-      <c r="C159" s="6" t="n"/>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="C159" s="17" t="n"/>
+      <c r="D159" s="6" t="n"/>
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
+      <c r="G159" s="6" t="inlineStr">
         <is>
           <t>2084024488</t>
         </is>
       </c>
-      <c r="G159" s="6" t="n"/>
-      <c r="H159" s="6" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I159" s="6" t="n"/>
-      <c r="J159" s="6" t="inlineStr">
+      <c r="H159" s="6" t="n"/>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="n"/>
+      <c r="K159" s="6" t="inlineStr">
         <is>
           <t>★フォールバック</t>
         </is>
@@ -6341,6 +6516,7 @@
       <c r="I160" s="13" t="n"/>
       <c r="J160" s="13" t="n"/>
       <c r="K160" s="14" t="n"/>
+      <c r="L160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -6353,30 +6529,31 @@
           <t>ティソ</t>
         </is>
       </c>
-      <c r="C161" s="4" t="n"/>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="C161" s="17" t="n"/>
+      <c r="D161" s="4" t="n"/>
+      <c r="E161" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
+      <c r="F161" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr">
+      <c r="G161" s="4" t="inlineStr">
         <is>
           <t>2084061410</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n"/>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="n"/>
+      <c r="H161" s="4" t="n"/>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J161" s="4" t="n"/>
+      <c r="K161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -6389,30 +6566,31 @@
           <t>ゼニス</t>
         </is>
       </c>
-      <c r="C162" s="4" t="n"/>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="C162" s="17" t="n"/>
+      <c r="D162" s="4" t="n"/>
+      <c r="E162" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F162" s="4" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>2084024517</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n"/>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="n"/>
+      <c r="H162" s="4" t="n"/>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J162" s="4" t="n"/>
+      <c r="K162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -6425,30 +6603,31 @@
           <t>オリス</t>
         </is>
       </c>
-      <c r="C163" s="4" t="n"/>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="C163" s="17" t="n"/>
+      <c r="D163" s="4" t="n"/>
+      <c r="E163" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>2084024537</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n"/>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="n"/>
+      <c r="H163" s="4" t="n"/>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J163" s="4" t="n"/>
+      <c r="K163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -6461,30 +6640,31 @@
           <t>ラドー</t>
         </is>
       </c>
-      <c r="C164" s="4" t="n"/>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="C164" s="17" t="n"/>
+      <c r="D164" s="4" t="n"/>
+      <c r="E164" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr">
+      <c r="G164" s="4" t="inlineStr">
         <is>
           <t>2084024519</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n"/>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="n"/>
+      <c r="H164" s="4" t="n"/>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J164" s="4" t="n"/>
+      <c r="K164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -6497,30 +6677,31 @@
           <t>ウブロ</t>
         </is>
       </c>
-      <c r="C165" s="4" t="n"/>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="C165" s="17" t="n"/>
+      <c r="D165" s="4" t="n"/>
+      <c r="E165" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
+      <c r="F165" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr">
+      <c r="G165" s="4" t="inlineStr">
         <is>
           <t>2084212696</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n"/>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I165" s="4" t="n"/>
+      <c r="H165" s="4" t="n"/>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J165" s="4" t="n"/>
+      <c r="K165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -6533,34 +6714,35 @@
           <t>オーデマ・ピゲ</t>
         </is>
       </c>
-      <c r="C166" s="4" t="n"/>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="C166" s="17" t="n"/>
+      <c r="D166" s="4" t="n"/>
+      <c r="E166" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F166" s="4" t="inlineStr">
+      <c r="G166" s="4" t="inlineStr">
         <is>
           <t>2084024547</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n"/>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H166" s="4" t="n"/>
       <c r="I166" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="J166" s="4" t="n"/>
+      <c r="K166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -6573,34 +6755,35 @@
           <t>ヴァシュロン・コンスタンタン</t>
         </is>
       </c>
-      <c r="C167" s="4" t="n"/>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="C167" s="17" t="n"/>
+      <c r="D167" s="4" t="n"/>
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E167" s="4" t="inlineStr">
+      <c r="F167" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F167" s="4" t="inlineStr">
+      <c r="G167" s="4" t="inlineStr">
         <is>
           <t>2084024530</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n"/>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H167" s="4" t="n"/>
       <c r="I167" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
           <t>VC</t>
         </is>
       </c>
-      <c r="J167" s="4" t="n"/>
+      <c r="K167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -6613,30 +6796,31 @@
           <t>ブレゲ</t>
         </is>
       </c>
-      <c r="C168" s="4" t="n"/>
-      <c r="D168" s="4" t="inlineStr">
+      <c r="C168" s="17" t="n"/>
+      <c r="D168" s="4" t="n"/>
+      <c r="E168" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr">
+      <c r="G168" s="4" t="inlineStr">
         <is>
           <t>2084024521</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n"/>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I168" s="4" t="n"/>
+      <c r="H168" s="4" t="n"/>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J168" s="4" t="n"/>
+      <c r="K168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -6649,30 +6833,31 @@
           <t>ブランパン</t>
         </is>
       </c>
-      <c r="C169" s="4" t="n"/>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="C169" s="17" t="n"/>
+      <c r="D169" s="4" t="n"/>
+      <c r="E169" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
+      <c r="F169" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr">
+      <c r="G169" s="4" t="inlineStr">
         <is>
           <t>2084024545</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n"/>
-      <c r="H169" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="n"/>
+      <c r="H169" s="4" t="n"/>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J169" s="4" t="n"/>
+      <c r="K169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -6685,30 +6870,31 @@
           <t>ピアジェ</t>
         </is>
       </c>
-      <c r="C170" s="4" t="n"/>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="C170" s="17" t="n"/>
+      <c r="D170" s="4" t="n"/>
+      <c r="E170" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E170" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr">
+      <c r="G170" s="4" t="inlineStr">
         <is>
           <t>2084024525</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n"/>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="n"/>
+      <c r="H170" s="4" t="n"/>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J170" s="4" t="n"/>
+      <c r="K170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -6721,34 +6907,35 @@
           <t>ジャガー・ルクルト</t>
         </is>
       </c>
-      <c r="C171" s="4" t="n"/>
-      <c r="D171" s="4" t="inlineStr">
+      <c r="C171" s="17" t="n"/>
+      <c r="D171" s="4" t="n"/>
+      <c r="E171" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
+      <c r="F171" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F171" s="4" t="inlineStr">
+      <c r="G171" s="4" t="inlineStr">
         <is>
           <t>2084024520</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n"/>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H171" s="4" t="n"/>
       <c r="I171" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
           <t>JLC</t>
         </is>
       </c>
-      <c r="J171" s="4" t="n"/>
+      <c r="K171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -6761,34 +6948,35 @@
           <t>ジラール・ペルゴ</t>
         </is>
       </c>
-      <c r="C172" s="4" t="n"/>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="C172" s="17" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
+      <c r="F172" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
+      <c r="G172" s="4" t="inlineStr">
         <is>
           <t>2084024532</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n"/>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H172" s="4" t="n"/>
       <c r="I172" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="J172" s="4" t="n"/>
+      <c r="K172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -6801,30 +6989,31 @@
           <t>ショパール</t>
         </is>
       </c>
-      <c r="C173" s="4" t="n"/>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="C173" s="17" t="n"/>
+      <c r="D173" s="4" t="n"/>
+      <c r="E173" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
+      <c r="F173" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
+      <c r="G173" s="4" t="inlineStr">
         <is>
           <t>2084024543</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n"/>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I173" s="4" t="n"/>
+      <c r="H173" s="4" t="n"/>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J173" s="4" t="n"/>
+      <c r="K173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -6837,34 +7026,35 @@
           <t>ティファニー</t>
         </is>
       </c>
-      <c r="C174" s="4" t="n"/>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="C174" s="17" t="n"/>
+      <c r="D174" s="4" t="n"/>
+      <c r="E174" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
+      <c r="F174" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F174" s="4" t="inlineStr">
+      <c r="G174" s="4" t="inlineStr">
         <is>
           <t>2084024527</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n"/>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H174" s="4" t="n"/>
       <c r="I174" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
           <t>Tiffany &amp; Co</t>
         </is>
       </c>
-      <c r="J174" s="4" t="n"/>
+      <c r="K174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -6877,30 +7067,31 @@
           <t>コーチ</t>
         </is>
       </c>
-      <c r="C175" s="4" t="n"/>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="C175" s="17" t="n"/>
+      <c r="D175" s="4" t="n"/>
+      <c r="E175" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E175" s="4" t="inlineStr">
+      <c r="F175" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
+      <c r="G175" s="4" t="inlineStr">
         <is>
           <t>2084024542</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n"/>
-      <c r="H175" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="n"/>
+      <c r="H175" s="4" t="n"/>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J175" s="4" t="n"/>
+      <c r="K175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -6913,30 +7104,31 @@
           <t>フォッシル</t>
         </is>
       </c>
-      <c r="C176" s="4" t="n"/>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="C176" s="17" t="n"/>
+      <c r="D176" s="4" t="n"/>
+      <c r="E176" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="F176" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="G176" s="4" t="inlineStr">
         <is>
           <t>2084024541</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n"/>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="n"/>
+      <c r="H176" s="4" t="n"/>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J176" s="4" t="n"/>
+      <c r="K176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -6949,30 +7141,31 @@
           <t>タイメックス</t>
         </is>
       </c>
-      <c r="C177" s="4" t="n"/>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="C177" s="17" t="n"/>
+      <c r="D177" s="4" t="n"/>
+      <c r="E177" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
+      <c r="F177" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="G177" s="4" t="inlineStr">
         <is>
           <t>2084024538</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n"/>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="n"/>
+      <c r="H177" s="4" t="n"/>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J177" s="4" t="n"/>
+      <c r="K177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -6985,30 +7178,31 @@
           <t>スカーゲン</t>
         </is>
       </c>
-      <c r="C178" s="4" t="n"/>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="C178" s="17" t="n"/>
+      <c r="D178" s="4" t="n"/>
+      <c r="E178" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr">
+      <c r="F178" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F178" s="4" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr">
         <is>
           <t>2084226881</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n"/>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="n"/>
+      <c r="H178" s="4" t="n"/>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J178" s="4" t="n"/>
+      <c r="K178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -7021,30 +7215,31 @@
           <t>スント</t>
         </is>
       </c>
-      <c r="C179" s="4" t="n"/>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="C179" s="17" t="n"/>
+      <c r="D179" s="4" t="n"/>
+      <c r="E179" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E179" s="4" t="inlineStr">
+      <c r="F179" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F179" s="4" t="inlineStr">
+      <c r="G179" s="4" t="inlineStr">
         <is>
           <t>2084062073</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n"/>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="n"/>
+      <c r="H179" s="4" t="n"/>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J179" s="4" t="n"/>
+      <c r="K179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -7057,30 +7252,31 @@
           <t>ビクトリノックス</t>
         </is>
       </c>
-      <c r="C180" s="4" t="n"/>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="C180" s="17" t="n"/>
+      <c r="D180" s="4" t="n"/>
+      <c r="E180" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
+      <c r="F180" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
+      <c r="G180" s="4" t="inlineStr">
         <is>
           <t>2084024546</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n"/>
-      <c r="H180" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="n"/>
+      <c r="H180" s="4" t="n"/>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J180" s="4" t="n"/>
+      <c r="K180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -7093,34 +7289,35 @@
           <t>アルマーニ</t>
         </is>
       </c>
-      <c r="C181" s="4" t="n"/>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="C181" s="17" t="n"/>
+      <c r="D181" s="4" t="n"/>
+      <c r="E181" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="G181" s="4" t="inlineStr">
         <is>
           <t>2084217132</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n"/>
-      <c r="H181" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H181" s="4" t="n"/>
       <c r="I181" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
           <t>EMPORIO ARMANI, GIORGIO ARMANI</t>
         </is>
       </c>
-      <c r="J181" s="4" t="n"/>
+      <c r="K181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -7133,30 +7330,31 @@
           <t>フェンディ</t>
         </is>
       </c>
-      <c r="C182" s="4" t="n"/>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="C182" s="17" t="n"/>
+      <c r="D182" s="4" t="n"/>
+      <c r="E182" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
+      <c r="F182" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F182" s="4" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>2084024518</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n"/>
-      <c r="H182" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="n"/>
+      <c r="H182" s="4" t="n"/>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J182" s="4" t="n"/>
+      <c r="K182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -7169,30 +7367,31 @@
           <t>ダンヒル</t>
         </is>
       </c>
-      <c r="C183" s="4" t="n"/>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="C183" s="17" t="n"/>
+      <c r="D183" s="4" t="n"/>
+      <c r="E183" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E183" s="4" t="inlineStr">
+      <c r="F183" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F183" s="4" t="inlineStr">
+      <c r="G183" s="4" t="inlineStr">
         <is>
           <t>2084051026</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n"/>
-      <c r="H183" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I183" s="4" t="n"/>
+      <c r="H183" s="4" t="n"/>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J183" s="4" t="n"/>
+      <c r="K183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -7205,30 +7404,31 @@
           <t>ポール・スミス</t>
         </is>
       </c>
-      <c r="C184" s="4" t="n"/>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="C184" s="17" t="n"/>
+      <c r="D184" s="4" t="n"/>
+      <c r="E184" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
+      <c r="F184" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F184" s="4" t="inlineStr">
+      <c r="G184" s="4" t="inlineStr">
         <is>
           <t>2084061863</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n"/>
-      <c r="H184" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I184" s="4" t="n"/>
+      <c r="H184" s="4" t="n"/>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J184" s="4" t="n"/>
+      <c r="K184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -7241,30 +7441,31 @@
           <t>ウェンガー</t>
         </is>
       </c>
-      <c r="C185" s="4" t="n"/>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="C185" s="17" t="n"/>
+      <c r="D185" s="4" t="n"/>
+      <c r="E185" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E185" s="4" t="inlineStr">
+      <c r="F185" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr">
+      <c r="G185" s="4" t="inlineStr">
         <is>
           <t>2084206922</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n"/>
-      <c r="H185" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I185" s="4" t="n"/>
+      <c r="H185" s="4" t="n"/>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J185" s="4" t="n"/>
+      <c r="K185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -7277,34 +7478,35 @@
           <t>ルイ・ヴィトン</t>
         </is>
       </c>
-      <c r="C186" s="4" t="n"/>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="C186" s="17" t="n"/>
+      <c r="D186" s="4" t="n"/>
+      <c r="E186" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E186" s="4" t="inlineStr">
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F186" s="4" t="inlineStr">
+      <c r="G186" s="4" t="inlineStr">
         <is>
           <t>2084051028</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n"/>
-      <c r="H186" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H186" s="4" t="n"/>
       <c r="I186" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="J186" s="4" t="n"/>
+      <c r="K186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -7317,30 +7519,31 @@
           <t>テクノス</t>
         </is>
       </c>
-      <c r="C187" s="4" t="n"/>
-      <c r="D187" s="4" t="inlineStr">
+      <c r="C187" s="17" t="n"/>
+      <c r="D187" s="4" t="n"/>
+      <c r="E187" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E187" s="4" t="inlineStr">
+      <c r="F187" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F187" s="4" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>2084214351</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n"/>
-      <c r="H187" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="n"/>
+      <c r="H187" s="4" t="n"/>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J187" s="4" t="n"/>
+      <c r="K187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -7353,30 +7556,31 @@
           <t>エルジン</t>
         </is>
       </c>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="inlineStr">
+      <c r="C188" s="17" t="n"/>
+      <c r="D188" s="4" t="n"/>
+      <c r="E188" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
+      <c r="F188" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F188" s="4" t="inlineStr">
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>2084024513</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n"/>
-      <c r="H188" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="n"/>
+      <c r="H188" s="4" t="n"/>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J188" s="4" t="n"/>
+      <c r="K188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -7389,30 +7593,31 @@
           <t>ヴェルサーチ</t>
         </is>
       </c>
-      <c r="C189" s="4" t="n"/>
-      <c r="D189" s="4" t="inlineStr">
+      <c r="C189" s="17" t="n"/>
+      <c r="D189" s="4" t="n"/>
+      <c r="E189" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F189" s="4" t="inlineStr">
+      <c r="G189" s="4" t="inlineStr">
         <is>
           <t>2084224440</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n"/>
-      <c r="H189" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="n"/>
+      <c r="H189" s="4" t="n"/>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J189" s="4" t="n"/>
+      <c r="K189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -7425,30 +7630,31 @@
           <t>モンブラン</t>
         </is>
       </c>
-      <c r="C190" s="4" t="n"/>
-      <c r="D190" s="4" t="inlineStr">
+      <c r="C190" s="17" t="n"/>
+      <c r="D190" s="4" t="n"/>
+      <c r="E190" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
+      <c r="F190" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="G190" s="4" t="inlineStr">
         <is>
           <t>2084229201</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n"/>
-      <c r="H190" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I190" s="4" t="n"/>
+      <c r="H190" s="4" t="n"/>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J190" s="4" t="n"/>
+      <c r="K190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -7461,30 +7667,31 @@
           <t>ヴィヴィアン ウエストウッド</t>
         </is>
       </c>
-      <c r="C191" s="4" t="n"/>
-      <c r="D191" s="4" t="inlineStr">
+      <c r="C191" s="17" t="n"/>
+      <c r="D191" s="4" t="n"/>
+      <c r="E191" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E191" s="4" t="inlineStr">
+      <c r="F191" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F191" s="4" t="inlineStr">
+      <c r="G191" s="4" t="inlineStr">
         <is>
           <t>2084024531</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n"/>
-      <c r="H191" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I191" s="4" t="n"/>
+      <c r="H191" s="4" t="n"/>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J191" s="4" t="n"/>
+      <c r="K191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -7497,34 +7704,35 @@
           <t>アニエスベー</t>
         </is>
       </c>
-      <c r="C192" s="4" t="n"/>
-      <c r="D192" s="4" t="inlineStr">
+      <c r="C192" s="17" t="n"/>
+      <c r="D192" s="4" t="n"/>
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F192" s="4" t="inlineStr">
+      <c r="G192" s="4" t="inlineStr">
         <is>
           <t>2084024511</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n"/>
-      <c r="H192" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H192" s="4" t="n"/>
       <c r="I192" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
           <t>agnes b.</t>
         </is>
       </c>
-      <c r="J192" s="4" t="n"/>
+      <c r="K192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -7537,34 +7745,35 @@
           <t>アディダス</t>
         </is>
       </c>
-      <c r="C193" s="4" t="n"/>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="C193" s="17" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
+      <c r="F193" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F193" s="4" t="inlineStr">
+      <c r="G193" s="4" t="inlineStr">
         <is>
           <t>2084301267</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n"/>
-      <c r="H193" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
+      <c r="H193" s="4" t="n"/>
       <c r="I193" s="4" t="inlineStr">
         <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
           <t>adidas</t>
         </is>
       </c>
-      <c r="J193" s="4" t="n"/>
+      <c r="K193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -7577,30 +7786,31 @@
           <t>ナイキ</t>
         </is>
       </c>
-      <c r="C194" s="4" t="n"/>
-      <c r="D194" s="4" t="inlineStr">
+      <c r="C194" s="17" t="n"/>
+      <c r="D194" s="4" t="n"/>
+      <c r="E194" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E194" s="4" t="inlineStr">
+      <c r="F194" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F194" s="4" t="inlineStr">
+      <c r="G194" s="4" t="inlineStr">
         <is>
           <t>2084216392</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n"/>
-      <c r="H194" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="n"/>
+      <c r="H194" s="4" t="n"/>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J194" s="4" t="n"/>
+      <c r="K194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -7613,30 +7823,31 @@
           <t>ポリス</t>
         </is>
       </c>
-      <c r="C195" s="4" t="n"/>
-      <c r="D195" s="4" t="inlineStr">
+      <c r="C195" s="17" t="n"/>
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E195" s="4" t="inlineStr">
+      <c r="F195" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F195" s="4" t="inlineStr">
+      <c r="G195" s="4" t="inlineStr">
         <is>
           <t>2084216393</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n"/>
-      <c r="H195" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="n"/>
+      <c r="H195" s="4" t="n"/>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J195" s="4" t="n"/>
+      <c r="K195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -7649,30 +7860,31 @@
           <t>ウォルサム</t>
         </is>
       </c>
-      <c r="C196" s="4" t="n"/>
-      <c r="D196" s="4" t="inlineStr">
+      <c r="C196" s="17" t="n"/>
+      <c r="D196" s="4" t="n"/>
+      <c r="E196" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E196" s="4" t="inlineStr">
+      <c r="F196" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F196" s="4" t="inlineStr">
+      <c r="G196" s="4" t="inlineStr">
         <is>
           <t>2084024540</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n"/>
-      <c r="H196" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="n"/>
+      <c r="H196" s="4" t="n"/>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J196" s="4" t="n"/>
+      <c r="K196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -7685,30 +7897,31 @@
           <t>ブローバ</t>
         </is>
       </c>
-      <c r="C197" s="4" t="n"/>
-      <c r="D197" s="4" t="inlineStr">
+      <c r="C197" s="17" t="n"/>
+      <c r="D197" s="4" t="n"/>
+      <c r="E197" s="4" t="inlineStr">
         <is>
           <t>（その他）</t>
         </is>
       </c>
-      <c r="E197" s="4" t="inlineStr">
+      <c r="F197" s="4" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr">
+      <c r="G197" s="4" t="inlineStr">
         <is>
           <t>2084024529</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n"/>
-      <c r="H197" s="4" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="n"/>
+      <c r="H197" s="4" t="n"/>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
       <c r="J197" s="4" t="n"/>
+      <c r="K197" s="4" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I197"/>
@@ -8775,7 +8988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -8923,113 +9136,123 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>model_number: 型番。カンマ区切りで複数指定可。優先度0の照合に使用</t>
+          <t>brand_aliases: ブランドの別名。カンマ区切りで複数指定可。例: HERMÈS, HERMÉS（AIが別表記で認識した場合にbrand_enの正規名に変換して照合）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>series_en: シリーズ英字。AIの認識結果と照合</t>
+          <t>model_number: 型番。カンマ区切りで複数指定可。優先度0の照合に使用</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>series_kana: シリーズのカタカナ表記</t>
+          <t>series_en: シリーズ英字。AIの認識結果と照合</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>category_id: ヤフオクカテゴリ番号</t>
+          <t>series_kana: シリーズのカタカナ表記</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>gender: 性別が固定のシリーズのみ記入（LUKIAはレディース等）</t>
+          <t>category_id: ヤフオクカテゴリ番号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>type: 基本「本体」のみ。パーツ・ベルト等は不要</t>
+          <t>gender: 性別が固定のシリーズのみ記入（LUKIAはレディース等）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>keywords: 英字の別名・略称。カンマ区切りで複数指定可。優先度1の照合に使用</t>
+          <t>type: 基本「本体」のみ。パーツ・ベルト等は不要</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>notes: メモ欄（システムは参照しない）</t>
+          <t>keywords: 英字の別名・略称。カンマ区切りで複数指定可。優先度1の照合に使用</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
+          <t>notes: メモ欄（システムは参照しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
           <t>additional_word: 出品時にタイトル等へ追加する単語</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="12" t="n"/>
-    </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>★ 各ブランドに「（その他）」行を必ず1行追加すること（黄色行）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>★ 性別不明ブランド（DIESEL等）はcategory_id空欄にすること（ピンク行）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>★ 性別不明ブランド（DIESEL等）はcategory_id空欄にすること（ピンク行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>★ 行の追加・削除は自由。Excelを編集するだけでルール変更可能</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>■ Sheet2「汎用カテゴリ」の使い方</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ブランドがSheet1に未登録だった場合のフォールバック先</t>
-        </is>
-      </c>
-    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>性別（メンズ/レディース）+ ムーブメント + 針タイプで該当カテゴリを検索</t>
+          <t>ブランドがSheet1に未登録だった場合のフォールバック先</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
+        <is>
+          <t>性別（メンズ/レディース）+ ムーブメント + 針タイプで該当カテゴリを検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>基本的にこのシートの編集は不要（ヤフオクの既存カテゴリ体系のため）</t>
         </is>

--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -7953,7 +7953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8916,64 +8916,146 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
+          <t>ユニセックス</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2針（時、分）</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2084223450</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ユニセックス</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>3針（時、分、秒）</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>2084223456</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ユニセックス</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>クロノグラフ</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>2084223462</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ユニセックス</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>2084053684</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>★クォーツフォールバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>【特殊カテゴリ】</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4" t="inlineStr">
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
         <is>
           <t>懐中時計 クォーツ</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2084062953</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr"/>
-      <c r="B46" s="4" t="inlineStr"/>
-      <c r="C46" s="4" t="inlineStr">
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
         <is>
           <t>懐中時計 自動巻き</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2084062955</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="4" t="inlineStr">
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
         <is>
           <t>懐中時計 手巻き</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2084062956</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -9227,8 +9309,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -9236,7 +9316,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>

--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -8583,7 +8583,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2084223429</t>
+          <t>2084223408</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2084223428</t>
+          <t>2084223407</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2084223432</t>
+          <t>2084223411</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2084223435</t>
+          <t>2084223414</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2084223438</t>
+          <t>2084223417</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2084223441</t>
+          <t>2084223420</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2084223444</t>
+          <t>2084223423</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>2084063360</t>
+          <t>2084053703</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">

--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2084223450</t>
+          <t>2084223429</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2084223456</t>
+          <t>2084223435</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2084223462</t>
+          <t>2084223441</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2084053684</t>
+          <t>2084063360</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">

--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -7953,7 +7953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7992,6 +7992,12 @@
         <is>
           <t>notes
 （備考）</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>additional_word
+（追加単語）</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -9281,7 +9287,7 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>additional_word: 出品時にタイトル等へ追加する単語</t>
+          <t>additional_word: 出品時にタイトル等へ追加する単語。ブランドまたは型番のどちらかが一致した行から取得される（優先度: ブランド+型番 &gt; 型番のみ &gt; ブランドのみ）</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9339,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>基本的にこのシートの編集は不要（ヤフオクの既存カテゴリ体系のため）</t>
+          <t>additional_word（追加単語）: 汎用カテゴリが使用された場合にタイトル末尾へ自動追記される単語。F列に記入</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>基本的にカテゴリ番号の編集は不要（ヤフオクの既存カテゴリ体系のため）。追加単語のみ必要に応じて記入</t>
         </is>
       </c>
     </row>
